--- a/Financial Analysis/Models (Automotive).xlsx
+++ b/Financial Analysis/Models (Automotive).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{394DB763-E1DA-46F2-8EF5-B9884AC45F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E6B13EA-5DB6-4C62-A6C1-F162B33F00D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{44A3A52B-B984-4465-AC96-672BE039DB0B}"/>
   </bookViews>
@@ -181,21 +181,6 @@
     <t>Kia</t>
   </si>
   <si>
-    <t>2023 Rev</t>
-  </si>
-  <si>
-    <t>2022 RevG</t>
-  </si>
-  <si>
-    <t>2023 RevG</t>
-  </si>
-  <si>
-    <t>2023 GM%</t>
-  </si>
-  <si>
-    <t>2023 OM%</t>
-  </si>
-  <si>
     <t>2025 E</t>
   </si>
   <si>
@@ -259,7 +244,22 @@
     <t>LCID US</t>
   </si>
   <si>
-    <t>2023 EV/R</t>
+    <t>2025 Rev</t>
+  </si>
+  <si>
+    <t>2025 EV/R</t>
+  </si>
+  <si>
+    <t>2025 GM%</t>
+  </si>
+  <si>
+    <t>2025 OM%</t>
+  </si>
+  <si>
+    <t>2024 RevG</t>
+  </si>
+  <si>
+    <t>2025 RevG</t>
   </si>
 </sst>
 </file>
@@ -279,7 +279,7 @@
     <numFmt numFmtId="173" formatCode="#,##0\ [$€-407]"/>
     <numFmt numFmtId="174" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -350,6 +350,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -399,7 +407,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -459,14 +467,26 @@
     <xf numFmtId="172" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="173" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="174" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="174" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -501,30 +521,30 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>256.58999999999997</v>
+            <v>312.60000000000002</v>
           </cell>
           <cell r="E3">
-            <v>45770</v>
+            <v>45862</v>
           </cell>
           <cell r="G3">
-            <v>45867</v>
+            <v>45945</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>826476.3899999999</v>
+            <v>1007509.8</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>29467</v>
+            <v>29562</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="9">
-          <cell r="AQ9">
-            <v>24578</v>
+        <row r="6">
+          <cell r="AW6">
+            <v>64034.32</v>
           </cell>
         </row>
         <row r="27">
@@ -535,16 +555,16 @@
             <v>7091</v>
           </cell>
           <cell r="AW27">
-            <v>4527.4714350000158</v>
+            <v>3108.4869984000024</v>
           </cell>
           <cell r="AX27">
-            <v>7975.9653982800055</v>
+            <v>6756.6394432400202</v>
           </cell>
           <cell r="AY27">
-            <v>8710.7820470256011</v>
+            <v>7545.3029727164021</v>
           </cell>
           <cell r="AZ27">
-            <v>9948.3296597538665</v>
+            <v>8985.0711792893107</v>
           </cell>
         </row>
         <row r="31">
@@ -562,7 +582,7 @@
         </row>
         <row r="37">
           <cell r="BJ37">
-            <v>-0.62575831274388716</v>
+            <v>-0.69705744731799135</v>
           </cell>
         </row>
         <row r="38">
@@ -600,84 +620,84 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>8</v>
+            <v>7.5670000000000002</v>
           </cell>
           <cell r="E3">
-            <v>45771</v>
+            <v>45868</v>
           </cell>
           <cell r="G3">
-            <v>45777</v>
+            <v>45960</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>30100.799999999999</v>
+            <v>21812.6342</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-3127</v>
+            <v>-10139</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>33227.800000000003</v>
+            <v>31951.6342</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="3">
-          <cell r="Q3">
+        <row r="10">
+          <cell r="Q10">
             <v>189544</v>
           </cell>
         </row>
-        <row r="17">
-          <cell r="Q17">
+        <row r="24">
+          <cell r="Q24">
             <v>18596</v>
           </cell>
-          <cell r="R17">
+          <cell r="R24">
             <v>5473</v>
           </cell>
-          <cell r="S17">
-            <v>-121.04400000000184</v>
-          </cell>
-          <cell r="T17">
-            <v>2322.7907304000009</v>
-          </cell>
-          <cell r="U17">
-            <v>4719.6040671360006</v>
-          </cell>
-          <cell r="V17">
-            <v>5964.6729261672017</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="Q21">
+          <cell r="S24">
+            <v>-3955.4684000000334</v>
+          </cell>
+          <cell r="T24">
+            <v>-980.07988364999983</v>
+          </cell>
+          <cell r="U24">
+            <v>1842.0949888019975</v>
+          </cell>
+          <cell r="V24">
+            <v>5262.873720354808</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="Q35">
             <v>5.5414495077731774E-2</v>
           </cell>
         </row>
-        <row r="22">
-          <cell r="Q22">
-            <v>0.20124087283163802</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="AF24">
-            <v>0.08</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="Q25">
-            <v>0.11805174524121048</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="AF30">
-            <v>1.3973121928006629</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="AF31" t="str">
+        <row r="36">
+          <cell r="S36">
+            <v>8.5394651372724173E-2</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="AF38">
+            <v>0.09</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="S39">
+            <v>-3.1254943975238522E-2</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="AF44">
+            <v>1.6974869917057078</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="AF45" t="str">
             <v>Heavily undervalued</v>
           </cell>
         </row>
@@ -762,18 +782,18 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>11.96</v>
+            <v>13.57</v>
           </cell>
           <cell r="E3">
-            <v>45713</v>
+            <v>45899</v>
           </cell>
           <cell r="G3">
-            <v>45790</v>
+            <v>45966</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>12653.68</v>
+            <v>16465.838000000003</v>
           </cell>
         </row>
         <row r="8">
@@ -783,14 +803,14 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>9394.68</v>
+            <v>13206.838000000003</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="5">
-          <cell r="X5">
-            <v>4434</v>
+          <cell r="Z5">
+            <v>5583</v>
           </cell>
         </row>
         <row r="21">
@@ -801,47 +821,49 @@
             <v>-4747</v>
           </cell>
           <cell r="Z21">
-            <v>-2737.1781026800018</v>
+            <v>-2883.1596</v>
           </cell>
           <cell r="AA21">
-            <v>-2431.7268265104008</v>
+            <v>-2176.9613879999993</v>
           </cell>
           <cell r="AB21">
-            <v>-2099.6875420206088</v>
+            <v>-1518.9675790080003</v>
           </cell>
           <cell r="AC21">
-            <v>-1692.1326230002155</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="W25">
+            <v>-1276.1137779020798</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="W27">
             <v>29.145454545454545</v>
           </cell>
-          <cell r="X25">
+          <cell r="X27">
             <v>1.6743063932448732</v>
           </cell>
         </row>
-        <row r="26">
-          <cell r="X26">
-            <v>-0.45782589084348219</v>
-          </cell>
-          <cell r="Y26">
-            <v>-0.2414486921529175</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="AN27">
+        <row r="30">
+          <cell r="Z30">
+            <v>0.10388679921189324</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="AN31">
             <v>0.09</v>
           </cell>
         </row>
-        <row r="34">
-          <cell r="AN34" t="str">
+        <row r="33">
+          <cell r="Z33">
+            <v>-0.53904703564391909</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="AN38" t="str">
             <v>Heavily overvalued</v>
           </cell>
         </row>
-        <row r="78">
-          <cell r="AN78">
-            <v>-1.0978041506643392</v>
+        <row r="82">
+          <cell r="AN82">
+            <v>-0.77098230893300101</v>
           </cell>
         </row>
       </sheetData>
@@ -864,88 +886,88 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>2.46</v>
+            <v>1.98</v>
           </cell>
           <cell r="E3">
-            <v>45771</v>
+            <v>45889</v>
           </cell>
           <cell r="G3">
-            <v>45783</v>
+            <v>45972</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>7457.49</v>
+            <v>6083.55</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>2028.8</v>
+            <v>1563.6</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>5428.69</v>
+            <v>4519.9500000000007</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="3">
-          <cell r="AB3">
-            <v>595.29999999999995</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="AB14">
+        <row r="6">
+          <cell r="AD6">
+            <v>1191.3249999999998</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="AB17">
             <v>-2828.3</v>
           </cell>
-          <cell r="AC14">
+          <cell r="AC17">
             <v>-2714.0000000000005</v>
           </cell>
-          <cell r="AD14">
-            <v>-2534.33</v>
-          </cell>
-          <cell r="AE14">
-            <v>-2333.4748500000001</v>
-          </cell>
-          <cell r="AF14">
-            <v>-1943.7248985000001</v>
-          </cell>
-          <cell r="AG14">
-            <v>-1535.5301804850001</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="AA18">
+          <cell r="AD17">
+            <v>-1573.4800000000002</v>
+          </cell>
+          <cell r="AE17">
+            <v>-1338.9207800000001</v>
+          </cell>
+          <cell r="AF17">
+            <v>-909.73493530000019</v>
+          </cell>
+          <cell r="AG17">
+            <v>-460.13275752800018</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="AA26">
             <v>21.44280442804428</v>
           </cell>
-          <cell r="AB18">
+          <cell r="AB26">
             <v>-2.1210128247287185E-2</v>
           </cell>
         </row>
-        <row r="19">
-          <cell r="AB19">
-            <v>-2.2523097597849824</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="AQ20">
-            <v>0.1</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="AB22">
-            <v>-5.2066185116747858</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="AQ26">
-            <v>-1.7560259481433871</v>
-          </cell>
-        </row>
         <row r="27">
-          <cell r="AQ27" t="str">
-            <v>Heavily overvalued</v>
+          <cell r="AD27">
+            <v>-0.6</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="AQ28">
+            <v>0.09</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="AD31">
+            <v>-2.3225232409292178</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="AQ34">
+            <v>-0.1348443553182711</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="AQ35" t="str">
+            <v>Slightly overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -968,80 +990,80 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>1.0980000000000001</v>
+            <v>0.71850000000000003</v>
           </cell>
           <cell r="E3">
-            <v>45635</v>
+            <v>45869</v>
           </cell>
           <cell r="G3">
-            <v>45715</v>
+            <v>45961</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>905.85</v>
+            <v>686.52674999999999</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-974.2</v>
+            <v>-1169.8</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="3">
-          <cell r="AH3">
-            <v>1632.8</v>
+          <cell r="AN3">
+            <v>1631.4170000000001</v>
           </cell>
         </row>
         <row r="15">
-          <cell r="AH15">
+          <cell r="AL15">
             <v>-228.10000000000014</v>
           </cell>
-          <cell r="AI15">
-            <v>-239.64460000000003</v>
-          </cell>
-          <cell r="AJ15">
-            <v>-137.36318280000003</v>
-          </cell>
-          <cell r="AK15">
-            <v>-45.433853162400069</v>
-          </cell>
-          <cell r="AL15">
-            <v>28.41758343130066</v>
-          </cell>
           <cell r="AM15">
-            <v>79.191899431941238</v>
+            <v>-323.49999999999989</v>
+          </cell>
+          <cell r="AN15">
+            <v>-169.45059199999997</v>
+          </cell>
+          <cell r="AO15">
+            <v>-24.605004735999863</v>
+          </cell>
+          <cell r="AP15">
+            <v>83.85838662611188</v>
+          </cell>
+          <cell r="AQ15">
+            <v>165.4102204171208</v>
           </cell>
         </row>
         <row r="19">
-          <cell r="AG19">
+          <cell r="AK19">
             <v>0.26129827444535758</v>
           </cell>
-          <cell r="AH19">
+          <cell r="AL19">
             <v>0.18190372783206654</v>
           </cell>
-          <cell r="AW19">
-            <v>0.08</v>
+          <cell r="BA19">
+            <v>0.1</v>
           </cell>
         </row>
         <row r="20">
-          <cell r="AH20">
-            <v>0.3914747672709456</v>
+          <cell r="AN20">
+            <v>0.37</v>
           </cell>
         </row>
         <row r="21">
-          <cell r="AH21">
-            <v>-6.8103870651641418E-2</v>
+          <cell r="AN21">
+            <v>-1.5595791879084222E-2</v>
           </cell>
         </row>
         <row r="25">
-          <cell r="AW25">
-            <v>-0.45006922200548305</v>
+          <cell r="BA25">
+            <v>-0.3508624801279675</v>
           </cell>
         </row>
         <row r="26">
-          <cell r="AW26" t="str">
+          <cell r="BA26" t="str">
             <v>Overvalued</v>
           </cell>
         </row>
@@ -1066,40 +1088,83 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>147.97</v>
+            <v>193.01</v>
           </cell>
           <cell r="E3">
-            <v>44256</v>
+            <v>45904</v>
           </cell>
           <cell r="G3">
-            <v>44328</v>
+            <v>45959</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>206714.09</v>
+            <v>251548.00289999999</v>
           </cell>
         </row>
         <row r="10">
           <cell r="D10">
-            <v>-146463.68690602612</v>
+            <v>-165794.88908367607</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
+        <row r="3">
+          <cell r="AO3">
+            <v>336849.65383318724</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="AL17">
+            <v>16541.824556671836</v>
+          </cell>
+          <cell r="AM17">
+            <v>33341.865012473871</v>
+          </cell>
+          <cell r="AN17">
+            <v>32129.215831703863</v>
+          </cell>
+          <cell r="AO17">
+            <v>31093.189943334906</v>
+          </cell>
+          <cell r="AP17">
+            <v>31960.129021656801</v>
+          </cell>
+          <cell r="AQ17">
+            <v>32363.77480878443</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="AN21">
+            <v>6.5225807774974331E-2</v>
+          </cell>
+          <cell r="AO21">
+            <v>4.0000000000000036E-2</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="AO22">
+            <v>0.19</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="AO23">
+            <v>9.2356294694349347E-2</v>
+          </cell>
+        </row>
         <row r="24">
-          <cell r="AB24">
+          <cell r="BA24">
             <v>0.05</v>
           </cell>
         </row>
         <row r="30">
-          <cell r="AB30">
-            <v>0.19392279537411672</v>
+          <cell r="BA30">
+            <v>0.7738605857035239</v>
           </cell>
         </row>
         <row r="31">
-          <cell r="AB31" t="str">
-            <v>Slightly undervalued</v>
+          <cell r="BA31" t="str">
+            <v>Heavily undervalued</v>
           </cell>
         </row>
       </sheetData>
@@ -1123,23 +1188,23 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>98.4</v>
+            <v>101.3</v>
           </cell>
           <cell r="E3">
-            <v>45782</v>
+            <v>45863</v>
           </cell>
           <cell r="G3">
-            <v>45863</v>
+            <v>45960</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>49327.920000000006</v>
+            <v>50781.69</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-187383</v>
+            <v>-193006</v>
           </cell>
         </row>
       </sheetData>
@@ -1157,16 +1222,16 @@
             <v>10721</v>
           </cell>
           <cell r="AQ14">
-            <v>11092.382387500042</v>
+            <v>10128.217992400052</v>
           </cell>
           <cell r="AR14">
-            <v>13656.542687899993</v>
+            <v>13477.080804900001</v>
           </cell>
           <cell r="AS14">
-            <v>13793.108114778999</v>
+            <v>13611.851612949</v>
           </cell>
           <cell r="AT14">
-            <v>13931.039195926793</v>
+            <v>13747.970129078481</v>
           </cell>
         </row>
         <row r="18">
@@ -1194,12 +1259,12 @@
         </row>
         <row r="28">
           <cell r="BD28">
-            <v>-0.33083021401817747</v>
+            <v>-0.53295190785462565</v>
           </cell>
         </row>
         <row r="29">
           <cell r="BD29" t="str">
-            <v>Overvalued</v>
+            <v>Heavily overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -1222,18 +1287,18 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>45.63</v>
+            <v>52.41</v>
           </cell>
           <cell r="E3">
-            <v>45782</v>
+            <v>45863</v>
           </cell>
           <cell r="G3">
-            <v>45860</v>
+            <v>45951</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>43868.682000000001</v>
+            <v>49899.561000000002</v>
           </cell>
         </row>
         <row r="8">
@@ -1243,7 +1308,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>149057.682</v>
+            <v>155088.56099999999</v>
           </cell>
         </row>
       </sheetData>
@@ -1298,12 +1363,12 @@
         </row>
         <row r="31">
           <cell r="BD31">
-            <v>-7.1310548587337763E-3</v>
+            <v>-0.1271295548656699</v>
           </cell>
         </row>
         <row r="32">
           <cell r="BD32" t="str">
-            <v>Fairly valued</v>
+            <v>Slightly overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -1326,23 +1391,23 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>9.77</v>
+            <v>10.67</v>
           </cell>
           <cell r="E3">
-            <v>45771</v>
+            <v>45869</v>
           </cell>
           <cell r="G3">
-            <v>45782</v>
+            <v>45952</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>38723.394999999997</v>
+            <v>42466.6</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-109060</v>
+            <v>-113353</v>
           </cell>
         </row>
       </sheetData>
@@ -1360,16 +1425,16 @@
             <v>5879</v>
           </cell>
           <cell r="AQ13">
-            <v>6741.3520640000006</v>
+            <v>1239.4415999999778</v>
           </cell>
           <cell r="AR13">
-            <v>7500.3985802800016</v>
+            <v>4261.1494255000007</v>
           </cell>
           <cell r="AS13">
-            <v>7575.4783179578044</v>
+            <v>6642.8283350600059</v>
           </cell>
           <cell r="AT13">
-            <v>7651.3092317717565</v>
+            <v>7185.6523113568019</v>
           </cell>
         </row>
         <row r="17">
@@ -1384,7 +1449,7 @@
         </row>
         <row r="20">
           <cell r="BD20">
-            <v>0.06</v>
+            <v>0.05</v>
           </cell>
         </row>
         <row r="21">
@@ -1397,7 +1462,7 @@
         </row>
         <row r="26">
           <cell r="BD26">
-            <v>-0.93051516092840769</v>
+            <v>-0.61304644993749069</v>
           </cell>
         </row>
         <row r="27">
@@ -1425,25 +1490,25 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>53.31</v>
+            <v>53.35</v>
           </cell>
           <cell r="E3">
-            <v>45771</v>
+            <v>45899</v>
           </cell>
           <cell r="G3">
-            <v>45777</v>
+            <v>45959</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>54035.016000000003</v>
+            <v>51370.715000000004</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="3">
-          <cell r="AO3">
-            <v>153218</v>
+          <cell r="AQ3">
+            <v>136129.82</v>
           </cell>
         </row>
         <row r="20">
@@ -1454,54 +1519,54 @@
             <v>10207</v>
           </cell>
           <cell r="AQ20">
-            <v>11285.477327999997</v>
+            <v>6865.0766200000116</v>
           </cell>
           <cell r="AR20">
-            <v>11271.009509279995</v>
+            <v>9707.9691296400015</v>
           </cell>
           <cell r="AS20">
-            <v>11314.895253652796</v>
+            <v>9880.0234676748005</v>
           </cell>
           <cell r="AT20">
-            <v>11357.547096230926</v>
+            <v>10945.714426085773</v>
           </cell>
         </row>
         <row r="24">
-          <cell r="AN24">
-            <v>0.12042451808533672</v>
-          </cell>
-          <cell r="AO24">
-            <v>2.1337581740735967E-2</v>
+          <cell r="AP24">
+            <v>-4.9759166677544431E-2</v>
+          </cell>
+          <cell r="AQ24">
+            <v>-6.5003914996497048E-2</v>
           </cell>
         </row>
         <row r="25">
-          <cell r="AO25">
-            <v>0.22437964207860694</v>
+          <cell r="AQ25">
+            <v>0.19067507765748909</v>
           </cell>
         </row>
         <row r="26">
-          <cell r="AO26">
-            <v>0.1283139056768787</v>
+          <cell r="AQ26">
+            <v>6.9121053711817232E-2</v>
           </cell>
         </row>
         <row r="27">
           <cell r="BD27">
-            <v>0.08</v>
+            <v>7.0000000000000007E-2</v>
           </cell>
         </row>
         <row r="29">
           <cell r="BD29">
-            <v>-91201</v>
+            <v>-83984</v>
           </cell>
         </row>
         <row r="33">
           <cell r="BD33">
-            <v>-0.13237746470634748</v>
+            <v>0.1368869007603799</v>
           </cell>
         </row>
         <row r="34">
           <cell r="BD34" t="str">
-            <v>Slightly overvalued</v>
+            <v>Slightly undervalued</v>
           </cell>
         </row>
       </sheetData>
@@ -1524,23 +1589,23 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>73.680000000000007</v>
+            <v>88.28</v>
           </cell>
           <cell r="E3">
-            <v>45771</v>
+            <v>45904</v>
           </cell>
           <cell r="G3">
-            <v>45784</v>
+            <v>45966</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>45843.695999999996</v>
+            <v>54362.824000000008</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-91974</v>
+            <v>-88259</v>
           </cell>
         </row>
       </sheetData>
@@ -1558,16 +1623,16 @@
             <v>7290</v>
           </cell>
           <cell r="AQ14">
-            <v>7978.5110799999984</v>
+            <v>7270.331340000007</v>
           </cell>
           <cell r="AR14">
-            <v>8996.7216356640001</v>
+            <v>9446.2380771600037</v>
           </cell>
           <cell r="AS14">
-            <v>9363.1411170839237</v>
+            <v>10846.165776798605</v>
           </cell>
           <cell r="AT14">
-            <v>9546.9610448283565</v>
+            <v>11071.284089391702</v>
           </cell>
         </row>
         <row r="18">
@@ -1579,28 +1644,28 @@
           </cell>
         </row>
         <row r="19">
-          <cell r="AO19">
-            <v>0.19092850068811174</v>
+          <cell r="AQ19">
+            <v>0.16677202510748795</v>
           </cell>
         </row>
         <row r="20">
-          <cell r="AO20">
-            <v>0.1188568341715006</v>
+          <cell r="AQ20">
+            <v>8.3169312663695386E-2</v>
           </cell>
         </row>
         <row r="21">
           <cell r="BD21">
-            <v>0.08</v>
+            <v>7.0000000000000007E-2</v>
           </cell>
         </row>
         <row r="27">
           <cell r="BD27">
-            <v>-0.51311441678656355</v>
+            <v>9.5647188673537054E-2</v>
           </cell>
         </row>
         <row r="28">
           <cell r="BD28" t="str">
-            <v>Heavily overvalued</v>
+            <v>Fairly valued</v>
           </cell>
         </row>
       </sheetData>
@@ -1612,6 +1677,9 @@
 <file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
       <sheetName val="Model"/>
@@ -1621,39 +1689,86 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>25.53</v>
+            <v>33.54</v>
+          </cell>
+          <cell r="E3">
+            <v>45904</v>
+          </cell>
+          <cell r="G3">
+            <v>45966</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>44080.097999999998</v>
+            <v>48593.869999999995</v>
           </cell>
         </row>
         <row r="10">
           <cell r="D10">
-            <v>-47632.850505777977</v>
+            <v>-38276.555023923451</v>
           </cell>
         </row>
         <row r="11">
           <cell r="D11">
-            <v>91712.948505777982</v>
+            <v>86870.425023923453</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="23">
-          <cell r="R23">
-            <v>0.06</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="R29">
-            <v>0.20695593367719556</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="R30" t="str">
-            <v>Slightly undervalued</v>
+        <row r="3">
+          <cell r="J3">
+            <v>146160.57011928028</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="H17">
+            <v>5865.9360469034309</v>
+          </cell>
+          <cell r="I17">
+            <v>6638.4488173057462</v>
+          </cell>
+          <cell r="J17">
+            <v>4895.8762045959938</v>
+          </cell>
+          <cell r="K17">
+            <v>5185.0613296044212</v>
+          </cell>
+          <cell r="L17">
+            <v>5495.7142404744263</v>
+          </cell>
+          <cell r="M17">
+            <v>5493.7143140376029</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="K21">
+            <v>0.21</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="K22">
+            <v>4.7337701119796835E-2</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="J26">
+            <v>6.1675912273269962E-2</v>
+          </cell>
+          <cell r="K26">
+            <v>3.0000000000000027E-2</v>
+          </cell>
+          <cell r="W26">
+            <v>7.0000000000000007E-2</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="W32">
+            <v>-0.33736259729222229</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="W33" t="str">
+            <v>Overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -1677,43 +1792,88 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>46.72</v>
+            <v>41.45</v>
           </cell>
           <cell r="E3">
-            <v>45771</v>
+            <v>45923</v>
           </cell>
           <cell r="G3">
-            <v>45776</v>
+            <v>45954</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>42561.919999999998</v>
+            <v>37760.950000000004</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>-5029</v>
+            <v>-2528</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>47590.92</v>
+            <v>40288.950000000004</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="3">
-          <cell r="N3">
+        <row r="30">
+          <cell r="V30">
             <v>40530</v>
           </cell>
         </row>
-        <row r="19">
-          <cell r="N19">
+        <row r="49">
+          <cell r="V49">
             <v>5156</v>
           </cell>
-          <cell r="O19">
-            <v>3596</v>
+          <cell r="W49">
+            <v>3593</v>
+          </cell>
+          <cell r="X49">
+            <v>2058.3172399999958</v>
+          </cell>
+          <cell r="Y49">
+            <v>3097.2513473999998</v>
+          </cell>
+          <cell r="Z49">
+            <v>3707.8589376360001</v>
+          </cell>
+          <cell r="AA49">
+            <v>4061.902063665601</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="W53">
+            <v>-1.1028867505551432E-2</v>
+          </cell>
+          <cell r="X53">
+            <v>-6.0456303170920433E-2</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="X54">
+            <v>0.21190611563067488</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="AK56">
+            <v>0.08</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="X57">
+            <v>7.9327525715133795E-2</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="AK62">
+            <v>0.32757142189307098</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="AK63" t="str">
+            <v>Undervalued</v>
           </cell>
         </row>
       </sheetData>
@@ -2100,16 +2260,16 @@
         <v>17</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>15</v>
@@ -2121,31 +2281,31 @@
         <v>34</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="U2" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="W2" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="V2" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>48</v>
-      </c>
       <c r="X2" s="4" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="Z2" s="4" t="s">
         <v>36</v>
@@ -2183,60 +2343,60 @@
       <c r="M3" s="4"/>
       <c r="N3" s="6">
         <f t="shared" ref="N3:U3" si="0">TRIMMEAN(N4:N1048576,80%)</f>
-        <v>12.369528111804408</v>
+        <v>15.016831977855155</v>
       </c>
       <c r="O3" s="6">
         <f t="shared" si="0"/>
-        <v>18.404425571240498</v>
+        <v>16.412502823367006</v>
       </c>
       <c r="P3" s="6">
         <f t="shared" si="0"/>
-        <v>15.893304142149864</v>
+        <v>19.635704216861978</v>
       </c>
       <c r="Q3" s="6">
         <f t="shared" si="0"/>
-        <v>14.811888645755193</v>
+        <v>15.513504835381363</v>
       </c>
       <c r="R3" s="6">
         <f t="shared" si="0"/>
-        <v>15.940354557707543</v>
+        <v>15.824896923557986</v>
       </c>
       <c r="S3" s="6">
         <f t="shared" si="0"/>
-        <v>15.713692866564791</v>
+        <v>13.25662183271748</v>
       </c>
       <c r="T3" s="4"/>
-      <c r="U3" s="28">
+      <c r="U3" s="27">
         <f t="shared" si="0"/>
-        <v>0.99521007588381571</v>
+        <v>0.96851754398012357</v>
       </c>
       <c r="V3" s="7">
         <f t="shared" ref="V3:AA3" si="1">TRIMMEAN(V4:V1048576,80%)</f>
-        <v>0.25913588833450635</v>
+        <v>0.19267638552711031</v>
       </c>
       <c r="W3" s="7">
         <f t="shared" si="1"/>
-        <v>0.10555819036287195</v>
+        <v>8.0724152757208303E-2</v>
       </c>
       <c r="X3" s="7">
         <f t="shared" si="1"/>
-        <v>0.18591561828002373</v>
+        <v>0.1831298971399147</v>
       </c>
       <c r="Y3" s="7">
         <f t="shared" si="1"/>
-        <v>6.2078930623954212E-2</v>
+        <v>5.6855532694324286E-2</v>
       </c>
       <c r="Z3" s="7">
         <f t="shared" si="1"/>
-        <v>6.9999999999999993E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AA3" s="7">
         <f t="shared" si="1"/>
-        <v>-0.32448460534404661</v>
-      </c>
-      <c r="AB3" s="8" t="e">
+        <v>-0.19797272187116063</v>
+      </c>
+      <c r="AB3" s="8" t="str">
         <f>INDEX(AB4:AB17,MODE(MATCH(AB4:AB17,AB4:AB17,0)))</f>
-        <v>#N/A</v>
+        <v>Heavily overvalued</v>
       </c>
       <c r="AC3" s="2"/>
       <c r="AE3" s="2"/>
@@ -2251,19 +2411,19 @@
       </c>
       <c r="D4" s="10">
         <f>[1]Main!$D$3</f>
-        <v>256.58999999999997</v>
+        <v>312.60000000000002</v>
       </c>
       <c r="E4" s="11">
         <f>[1]Main!$D$5</f>
-        <v>826476.3899999999</v>
+        <v>1007509.8</v>
       </c>
       <c r="F4" s="11">
         <f>[1]Main!$D$8</f>
-        <v>29467</v>
+        <v>29562</v>
       </c>
       <c r="G4" s="11">
         <f>E4-F4</f>
-        <v>797009.3899999999</v>
+        <v>977947.8</v>
       </c>
       <c r="H4" s="11">
         <f>[1]Model!AU$27</f>
@@ -2275,51 +2435,51 @@
       </c>
       <c r="J4" s="11">
         <f>[1]Model!AW$27</f>
-        <v>4527.4714350000158</v>
+        <v>3108.4869984000024</v>
       </c>
       <c r="K4" s="11">
         <f>[1]Model!AX$27</f>
-        <v>7975.9653982800055</v>
+        <v>6756.6394432400202</v>
       </c>
       <c r="L4" s="11">
         <f>[1]Model!AY$27</f>
-        <v>8710.7820470256011</v>
+        <v>7545.3029727164021</v>
       </c>
       <c r="M4" s="11">
         <f>[1]Model!AZ$27</f>
-        <v>9948.3296597538665</v>
+        <v>8985.0711792893107</v>
       </c>
       <c r="N4" s="12">
         <f t="shared" ref="N4:S4" si="2">$G4/H4</f>
-        <v>53.144588250983524</v>
+        <v>65.209561912382483</v>
       </c>
       <c r="O4" s="12">
         <f t="shared" si="2"/>
-        <v>112.39731913693413</v>
+        <v>137.91394725708645</v>
       </c>
       <c r="P4" s="12">
         <f t="shared" si="2"/>
-        <v>176.03852424968355</v>
+        <v>314.60572313906039</v>
       </c>
       <c r="Q4" s="12">
         <f t="shared" si="2"/>
-        <v>99.926385108424967</v>
+        <v>144.73878741279162</v>
       </c>
       <c r="R4" s="12">
         <f t="shared" si="2"/>
-        <v>91.496881186706787</v>
+        <v>129.61014336153644</v>
       </c>
       <c r="S4" s="12">
         <f t="shared" si="2"/>
-        <v>80.114895390360317</v>
+        <v>108.84140820767014</v>
       </c>
       <c r="T4" s="13">
-        <f>[1]Model!$AQ$9</f>
-        <v>24578</v>
-      </c>
-      <c r="U4" s="27">
+        <f>[1]Model!$AW$6</f>
+        <v>64034.32</v>
+      </c>
+      <c r="U4" s="26">
         <f>G4/T4</f>
-        <v>32.42775612336235</v>
+        <v>15.272244633815118</v>
       </c>
       <c r="V4" s="14">
         <f>[1]Model!$AP$36</f>
@@ -2329,11 +2489,11 @@
         <f>[1]Model!$AQ$36</f>
         <v>0.14528823258046342</v>
       </c>
-      <c r="X4" s="14">
+      <c r="X4" s="32">
         <f>[1]Model!$AU$42</f>
         <v>0.18248891736331416</v>
       </c>
-      <c r="Y4" s="14">
+      <c r="Y4" s="32">
         <f>[1]Model!$AU$45</f>
         <v>9.1874799789197395E-2</v>
       </c>
@@ -2343,7 +2503,7 @@
       </c>
       <c r="AA4" s="14">
         <f>[1]Model!$BJ$37</f>
-        <v>-0.62575831274388716</v>
+        <v>-0.69705744731799135</v>
       </c>
       <c r="AB4" s="14" t="str">
         <f>[1]Model!$BJ$38</f>
@@ -2354,11 +2514,11 @@
       </c>
       <c r="AE4" s="16">
         <f>[1]Main!$E$3</f>
-        <v>45770</v>
+        <v>45862</v>
       </c>
       <c r="AF4" s="16">
         <f>[1]Main!$G$3</f>
-        <v>45867</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="5" spans="2:32" x14ac:dyDescent="0.3">
@@ -2370,52 +2530,114 @@
       </c>
       <c r="D5" s="10">
         <f>[2]Main!$D$3</f>
-        <v>147.97</v>
+        <v>193.01</v>
       </c>
       <c r="E5" s="11">
         <f>[2]Main!$D$5</f>
-        <v>206714.09</v>
+        <v>251548.00289999999</v>
       </c>
       <c r="F5" s="11">
         <f>[2]Main!$D$10</f>
-        <v>-146463.68690602612</v>
+        <v>-165794.88908367607</v>
       </c>
       <c r="G5" s="11">
         <f>E5-F5</f>
-        <v>353177.77690602612</v>
-      </c>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="13"/>
-      <c r="U5" s="13"/>
-      <c r="V5" s="14"/>
-      <c r="W5" s="14"/>
+        <v>417342.89198367606</v>
+      </c>
+      <c r="H5" s="11">
+        <f>[2]Model!AL$17</f>
+        <v>16541.824556671836</v>
+      </c>
+      <c r="I5" s="11">
+        <f>[2]Model!AM$17</f>
+        <v>33341.865012473871</v>
+      </c>
+      <c r="J5" s="11">
+        <f>[2]Model!AN$17</f>
+        <v>32129.215831703863</v>
+      </c>
+      <c r="K5" s="11">
+        <f>[2]Model!AO$17</f>
+        <v>31093.189943334906</v>
+      </c>
+      <c r="L5" s="11">
+        <f>[2]Model!AP$17</f>
+        <v>31960.129021656801</v>
+      </c>
+      <c r="M5" s="11">
+        <f>[2]Model!AQ$17</f>
+        <v>32363.77480878443</v>
+      </c>
+      <c r="N5" s="12">
+        <f t="shared" ref="N5" si="3">$G5/H5</f>
+        <v>25.229556180690395</v>
+      </c>
+      <c r="O5" s="12">
+        <f t="shared" ref="O5" si="4">$G5/I5</f>
+        <v>12.517083007430436</v>
+      </c>
+      <c r="P5" s="12">
+        <f t="shared" ref="P5" si="5">$G5/J5</f>
+        <v>12.989513786136614</v>
+      </c>
+      <c r="Q5" s="12">
+        <f t="shared" ref="Q5" si="6">$G5/K5</f>
+        <v>13.422324719472442</v>
+      </c>
+      <c r="R5" s="12">
+        <f t="shared" ref="R5" si="7">$G5/L5</f>
+        <v>13.058235519039252</v>
+      </c>
+      <c r="S5" s="12">
+        <f t="shared" ref="S5" si="8">$G5/M5</f>
+        <v>12.895371273884825</v>
+      </c>
+      <c r="T5" s="13">
+        <f>[2]Model!$AO$3</f>
+        <v>336849.65383318724</v>
+      </c>
+      <c r="U5" s="26">
+        <f>G5/T5</f>
+        <v>1.2389589457329537</v>
+      </c>
+      <c r="V5" s="14">
+        <f>[2]Model!AN$21</f>
+        <v>6.5225807774974331E-2</v>
+      </c>
+      <c r="W5" s="14">
+        <f>[2]Model!AO$21</f>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="X5" s="14">
+        <f>[2]Model!$AO$22</f>
+        <v>0.19</v>
+      </c>
+      <c r="Y5" s="14">
+        <f>[2]Model!$AO$23</f>
+        <v>9.2356294694349347E-2</v>
+      </c>
       <c r="Z5" s="14">
-        <f>[2]Model!$AB$24</f>
+        <f>[2]Model!$BA$24</f>
         <v>0.05</v>
       </c>
       <c r="AA5" s="14">
-        <f>[2]Model!$AB$30</f>
-        <v>0.19392279537411672</v>
+        <f>[2]Model!$BA$30</f>
+        <v>0.7738605857035239</v>
       </c>
       <c r="AB5" s="14" t="str">
-        <f>[2]Model!$AB$31</f>
-        <v>Slightly undervalued</v>
+        <f>[2]Model!$BA$31</f>
+        <v>Heavily undervalued</v>
       </c>
       <c r="AC5" s="15">
         <v>1937</v>
       </c>
       <c r="AE5" s="16">
         <f>[2]Main!$E$3</f>
-        <v>44256</v>
+        <v>45904</v>
       </c>
       <c r="AF5" s="16">
         <f>[2]Main!$G$3</f>
-        <v>44328</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="6" spans="2:32" x14ac:dyDescent="0.3">
@@ -2427,19 +2649,19 @@
       </c>
       <c r="D6" s="17">
         <f>[3]Main!$D$3</f>
-        <v>98.4</v>
+        <v>101.3</v>
       </c>
       <c r="E6" s="11">
         <f>[3]Main!$D$5</f>
-        <v>49327.920000000006</v>
+        <v>50781.69</v>
       </c>
       <c r="F6" s="11">
         <f>[3]Main!$D$8</f>
-        <v>-187383</v>
+        <v>-193006</v>
       </c>
       <c r="G6" s="11">
         <f>E6-F6</f>
-        <v>236710.92</v>
+        <v>243787.69</v>
       </c>
       <c r="H6" s="11">
         <f>[3]Model!AO14</f>
@@ -2451,51 +2673,51 @@
       </c>
       <c r="J6" s="11">
         <f>[3]Model!AQ14</f>
-        <v>11092.382387500042</v>
+        <v>10128.217992400052</v>
       </c>
       <c r="K6" s="11">
         <f>[3]Model!AR14</f>
-        <v>13656.542687899993</v>
+        <v>13477.080804900001</v>
       </c>
       <c r="L6" s="11">
         <f>[3]Model!AS14</f>
-        <v>13793.108114778999</v>
+        <v>13611.851612949</v>
       </c>
       <c r="M6" s="11">
         <f>[3]Model!AT14</f>
-        <v>13931.039195926793</v>
+        <v>13747.970129078481</v>
       </c>
       <c r="N6" s="12">
-        <f t="shared" ref="N6:S10" si="3">$G6/H6</f>
-        <v>14.782421782301881</v>
+        <f t="shared" ref="N6:S10" si="9">$G6/H6</f>
+        <v>15.224360831824143</v>
       </c>
       <c r="O6" s="12">
-        <f t="shared" si="3"/>
-        <v>22.079182912041787</v>
+        <f t="shared" si="9"/>
+        <v>22.739267792183565</v>
       </c>
       <c r="P6" s="12">
-        <f t="shared" si="3"/>
-        <v>21.339953107526163</v>
+        <f t="shared" si="9"/>
+        <v>24.070146414989473</v>
       </c>
       <c r="Q6" s="12">
-        <f t="shared" si="3"/>
-        <v>17.333151252822667</v>
+        <f t="shared" si="9"/>
+        <v>18.089057528790924</v>
       </c>
       <c r="R6" s="12">
-        <f t="shared" si="3"/>
-        <v>17.161535893883823</v>
+        <f t="shared" si="9"/>
+        <v>17.909957949297947</v>
       </c>
       <c r="S6" s="12">
-        <f t="shared" si="3"/>
-        <v>16.991619696914672</v>
-      </c>
-      <c r="T6" s="18">
+        <f t="shared" si="9"/>
+        <v>17.732631632968275</v>
+      </c>
+      <c r="T6" s="29">
         <f>[3]Model!$AO$3</f>
         <v>322284</v>
       </c>
-      <c r="U6" s="27">
-        <f t="shared" ref="U6:U10" si="4">G6/T6</f>
-        <v>0.73447927914510192</v>
+      <c r="U6" s="31">
+        <f t="shared" ref="U6:U11" si="10">G6/T6</f>
+        <v>0.75643745888719272</v>
       </c>
       <c r="V6" s="14">
         <f>[3]Model!$AN$23</f>
@@ -2505,11 +2727,11 @@
         <f>[3]Model!$AO$23</f>
         <v>0.15418003667201474</v>
       </c>
-      <c r="X6" s="14">
+      <c r="X6" s="32">
         <f>[3]Model!$AO$18</f>
         <v>0.18934231919673331</v>
       </c>
-      <c r="Y6" s="14">
+      <c r="Y6" s="32">
         <f>[3]Model!$AO$19</f>
         <v>7.0050017996549627E-2</v>
       </c>
@@ -2519,22 +2741,22 @@
       </c>
       <c r="AA6" s="14">
         <f>[3]Model!$BD$28</f>
-        <v>-0.33083021401817747</v>
+        <v>-0.53295190785462565</v>
       </c>
       <c r="AB6" s="14" t="str">
         <f>[3]Model!$BD$29</f>
-        <v>Overvalued</v>
+        <v>Heavily overvalued</v>
       </c>
       <c r="AC6" s="15">
         <v>1937</v>
       </c>
       <c r="AE6" s="16">
         <f>[3]Main!$E$3</f>
-        <v>45782</v>
+        <v>45863</v>
       </c>
       <c r="AF6" s="16">
         <f>[3]Main!$G$3</f>
-        <v>45863</v>
+        <v>45960</v>
       </c>
     </row>
     <row r="7" spans="2:32" x14ac:dyDescent="0.3">
@@ -2546,11 +2768,11 @@
       </c>
       <c r="D7" s="10">
         <f>[4]Main!$D$3</f>
-        <v>45.63</v>
+        <v>52.41</v>
       </c>
       <c r="E7" s="11">
         <f>[4]Main!$D$5</f>
-        <v>43868.682000000001</v>
+        <v>49899.561000000002</v>
       </c>
       <c r="F7" s="11">
         <f>[4]Main!$D$8</f>
@@ -2558,7 +2780,7 @@
       </c>
       <c r="G7" s="11">
         <f>[4]Main!$D$9</f>
-        <v>149057.682</v>
+        <v>155088.56099999999</v>
       </c>
       <c r="H7" s="11">
         <f>[4]Model!AO$16</f>
@@ -2585,36 +2807,36 @@
         <v>11083.806976747897</v>
       </c>
       <c r="N7" s="12">
-        <f t="shared" si="3"/>
-        <v>14.717385663507109</v>
+        <f t="shared" si="9"/>
+        <v>15.312851599526065</v>
       </c>
       <c r="O7" s="12">
-        <f t="shared" si="3"/>
-        <v>24.805738392411381</v>
+        <f t="shared" si="9"/>
+        <v>25.809379430853717</v>
       </c>
       <c r="P7" s="12">
-        <f t="shared" si="3"/>
-        <v>14.512997378942682</v>
+        <f t="shared" si="9"/>
+        <v>15.10019375785672</v>
       </c>
       <c r="Q7" s="12">
-        <f t="shared" si="3"/>
-        <v>14.117087557763579</v>
+        <f t="shared" si="9"/>
+        <v>14.688265411537513</v>
       </c>
       <c r="R7" s="12">
-        <f t="shared" si="3"/>
-        <v>13.765527496691263</v>
+        <f t="shared" si="9"/>
+        <v>14.322481218162107</v>
       </c>
       <c r="S7" s="12">
-        <f t="shared" si="3"/>
-        <v>13.448238706493159</v>
-      </c>
-      <c r="T7" s="13">
+        <f t="shared" si="9"/>
+        <v>13.992354912472912</v>
+      </c>
+      <c r="T7" s="28">
         <f>[4]Model!$AO$3</f>
         <v>171842</v>
       </c>
-      <c r="U7" s="27">
-        <f t="shared" si="4"/>
-        <v>0.86741123823046751</v>
+      <c r="U7" s="31">
+        <f t="shared" si="10"/>
+        <v>0.90250672710978685</v>
       </c>
       <c r="V7" s="14">
         <f>[4]Model!AN$23</f>
@@ -2624,11 +2846,11 @@
         <f>[4]Model!AO$23</f>
         <v>9.63856190385044E-2</v>
       </c>
-      <c r="X7" s="14">
+      <c r="X7" s="32">
         <f>[4]Model!$AO$20</f>
         <v>0.17755845485969671</v>
       </c>
-      <c r="Y7" s="14">
+      <c r="Y7" s="32">
         <f>[4]Model!$AO$21</f>
         <v>5.4107843251358805E-2</v>
       </c>
@@ -2638,22 +2860,22 @@
       </c>
       <c r="AA7" s="14">
         <f>[4]Model!$BD$31</f>
-        <v>-7.1310548587337763E-3</v>
+        <v>-0.1271295548656699</v>
       </c>
       <c r="AB7" s="14" t="str">
         <f>[4]Model!$BD$32</f>
-        <v>Fairly valued</v>
+        <v>Slightly overvalued</v>
       </c>
       <c r="AC7" s="15">
         <v>1908</v>
       </c>
       <c r="AE7" s="16">
         <f>[4]Main!$E$3</f>
-        <v>45782</v>
+        <v>45863</v>
       </c>
       <c r="AF7" s="16">
         <f>[4]Main!$G$3</f>
-        <v>45860</v>
+        <v>45951</v>
       </c>
     </row>
     <row r="8" spans="2:32" x14ac:dyDescent="0.3">
@@ -2665,19 +2887,19 @@
       </c>
       <c r="D8" s="10">
         <f>[5]Main!$D$3</f>
-        <v>9.77</v>
+        <v>10.67</v>
       </c>
       <c r="E8" s="11">
         <f>[5]Main!$D$5</f>
-        <v>38723.394999999997</v>
+        <v>42466.6</v>
       </c>
       <c r="F8" s="11">
         <f>[5]Main!$D$8</f>
-        <v>-109060</v>
+        <v>-113353</v>
       </c>
       <c r="G8" s="11">
         <f>E8-F8</f>
-        <v>147783.39499999999</v>
+        <v>155819.6</v>
       </c>
       <c r="H8" s="11">
         <f>[5]Model!AO$13</f>
@@ -2689,51 +2911,51 @@
       </c>
       <c r="J8" s="11">
         <f>[5]Model!AQ$13</f>
-        <v>6741.3520640000006</v>
+        <v>1239.4415999999778</v>
       </c>
       <c r="K8" s="11">
         <f>[5]Model!AR$13</f>
-        <v>7500.3985802800016</v>
+        <v>4261.1494255000007</v>
       </c>
       <c r="L8" s="11">
         <f>[5]Model!AS$13</f>
-        <v>7575.4783179578044</v>
+        <v>6642.8283350600059</v>
       </c>
       <c r="M8" s="11">
         <f>[5]Model!AT$13</f>
-        <v>7651.3092317717565</v>
+        <v>7185.6523113568019</v>
       </c>
       <c r="N8" s="12">
-        <f t="shared" si="3"/>
-        <v>33.996640211640212</v>
+        <f t="shared" si="9"/>
+        <v>35.845318610536005</v>
       </c>
       <c r="O8" s="12">
-        <f t="shared" si="3"/>
-        <v>25.137505528151046</v>
+        <f t="shared" si="9"/>
+        <v>26.504439530532405</v>
       </c>
       <c r="P8" s="12">
-        <f t="shared" si="3"/>
-        <v>21.921922130308129</v>
+        <f t="shared" si="9"/>
+        <v>125.71758120753958</v>
       </c>
       <c r="Q8" s="12">
-        <f t="shared" si="3"/>
-        <v>19.703405548146616</v>
+        <f t="shared" si="9"/>
+        <v>36.567504314100937</v>
       </c>
       <c r="R8" s="12">
-        <f t="shared" si="3"/>
-        <v>19.508127249163508</v>
+        <f t="shared" si="9"/>
+        <v>23.456815702673499</v>
       </c>
       <c r="S8" s="12">
-        <f t="shared" si="3"/>
-        <v>19.314785290122028</v>
-      </c>
-      <c r="T8" s="13">
+        <f t="shared" si="9"/>
+        <v>21.684823207174908</v>
+      </c>
+      <c r="T8" s="28">
         <f>[5]Model!$AO$3</f>
         <v>176191</v>
       </c>
-      <c r="U8" s="27">
-        <f t="shared" si="4"/>
-        <v>0.83876812663529909</v>
+      <c r="U8" s="31">
+        <f t="shared" si="10"/>
+        <v>0.88437888427899269</v>
       </c>
       <c r="V8" s="14">
         <f>[5]Model!$AN$21</f>
@@ -2743,21 +2965,21 @@
         <f>[5]Model!$AO$21</f>
         <v>0.1147307616872395</v>
       </c>
-      <c r="X8" s="14">
+      <c r="X8" s="32">
         <f>[5]Model!$AO$17</f>
         <v>0.14552956734452951</v>
       </c>
-      <c r="Y8" s="14">
+      <c r="Y8" s="32">
         <f>[5]Model!$AO$18</f>
         <v>3.0977745741836985E-2</v>
       </c>
       <c r="Z8" s="14">
         <f>[5]Model!$BD$20</f>
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AA8" s="14">
         <f>[5]Model!$BD$26</f>
-        <v>-0.93051516092840769</v>
+        <v>-0.61304644993749069</v>
       </c>
       <c r="AB8" s="14" t="str">
         <f>[5]Model!$BD$27</f>
@@ -2768,11 +2990,11 @@
       </c>
       <c r="AE8" s="16">
         <f>[5]Main!$E$3</f>
-        <v>45771</v>
+        <v>45869</v>
       </c>
       <c r="AF8" s="16">
         <f>[5]Main!$G$3</f>
-        <v>45782</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="9" spans="2:32" x14ac:dyDescent="0.3">
@@ -2780,23 +3002,23 @@
         <v>13</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D9" s="17">
         <f>[6]Main!$D$3</f>
-        <v>53.31</v>
+        <v>53.35</v>
       </c>
       <c r="E9" s="11">
         <f>[6]Main!$D$5</f>
-        <v>54035.016000000003</v>
+        <v>51370.715000000004</v>
       </c>
       <c r="F9" s="11">
         <f>[6]Model!$BD$29</f>
-        <v>-91201</v>
+        <v>-83984</v>
       </c>
       <c r="G9" s="11">
         <f>E9-F9</f>
-        <v>145236.016</v>
+        <v>135354.715</v>
       </c>
       <c r="H9" s="11">
         <f>[6]Model!AO20</f>
@@ -2808,90 +3030,90 @@
       </c>
       <c r="J9" s="11">
         <f>[6]Model!AQ20</f>
-        <v>11285.477327999997</v>
+        <v>6865.0766200000116</v>
       </c>
       <c r="K9" s="11">
         <f>[6]Model!AR20</f>
-        <v>11271.009509279995</v>
+        <v>9707.9691296400015</v>
       </c>
       <c r="L9" s="11">
         <f>[6]Model!AS20</f>
-        <v>11314.895253652796</v>
+        <v>9880.0234676748005</v>
       </c>
       <c r="M9" s="11">
         <f>[6]Model!AT20</f>
-        <v>11357.547096230926</v>
+        <v>10945.714426085773</v>
       </c>
       <c r="N9" s="12">
-        <f t="shared" ref="N9:S9" si="5">$G9/H9</f>
-        <v>10.184139681649253</v>
+        <f t="shared" ref="N9:S9" si="11">$G9/H9</f>
+        <v>9.491249912348362</v>
       </c>
       <c r="O9" s="12">
-        <f t="shared" si="5"/>
-        <v>14.229060056823748</v>
+        <f t="shared" si="11"/>
+        <v>13.260969432742236</v>
       </c>
       <c r="P9" s="12">
-        <f t="shared" si="5"/>
-        <v>12.869284282700217</v>
+        <f t="shared" si="11"/>
+        <v>19.71641723643279</v>
       </c>
       <c r="Q9" s="12">
-        <f t="shared" si="5"/>
-        <v>12.885803696680391</v>
+        <f t="shared" si="11"/>
+        <v>13.942639618284337</v>
       </c>
       <c r="R9" s="12">
-        <f t="shared" si="5"/>
-        <v>12.835825055747939</v>
+        <f t="shared" si="11"/>
+        <v>13.699837398448492</v>
       </c>
       <c r="S9" s="12">
-        <f t="shared" si="5"/>
-        <v>12.787621725838802</v>
+        <f t="shared" si="11"/>
+        <v>12.366000950785205</v>
       </c>
       <c r="T9" s="18">
-        <f>[6]Model!$AO$3</f>
-        <v>153218</v>
-      </c>
-      <c r="U9" s="27">
-        <f t="shared" si="4"/>
-        <v>0.94790439765562795</v>
+        <f>[6]Model!$AQ$3</f>
+        <v>136129.82</v>
+      </c>
+      <c r="U9" s="26">
+        <f t="shared" si="10"/>
+        <v>0.99430613365976672</v>
       </c>
       <c r="V9" s="14">
-        <f>[6]Model!$AN$24</f>
-        <v>0.12042451808533672</v>
+        <f>[6]Model!AP$24</f>
+        <v>-4.9759166677544431E-2</v>
       </c>
       <c r="W9" s="14">
-        <f>[6]Model!$AO$24</f>
-        <v>2.1337581740735967E-2</v>
+        <f>[6]Model!AQ$24</f>
+        <v>-6.5003914996497048E-2</v>
       </c>
       <c r="X9" s="14">
-        <f>[6]Model!$AO$25</f>
-        <v>0.22437964207860694</v>
+        <f>[6]Model!$AQ$25</f>
+        <v>0.19067507765748909</v>
       </c>
       <c r="Y9" s="14">
-        <f>[6]Model!$AO$26</f>
-        <v>0.1283139056768787</v>
+        <f>[6]Model!$AQ$26</f>
+        <v>6.9121053711817232E-2</v>
       </c>
       <c r="Z9" s="14">
         <f>[6]Model!$BD$27</f>
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AA9" s="14">
         <f>[6]Model!$BD$33</f>
-        <v>-0.13237746470634748</v>
+        <v>0.1368869007603799</v>
       </c>
       <c r="AB9" s="14" t="str">
         <f>[6]Model!$BD$34</f>
-        <v>Slightly overvalued</v>
+        <v>Slightly undervalued</v>
       </c>
       <c r="AC9" s="15">
         <v>1926</v>
       </c>
       <c r="AE9" s="16">
         <f>[6]Main!$E$3</f>
-        <v>45771</v>
+        <v>45899</v>
       </c>
       <c r="AF9" s="16">
         <f>[6]Main!$G$3</f>
-        <v>45777</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="10" spans="2:32" x14ac:dyDescent="0.3">
@@ -2903,19 +3125,19 @@
       </c>
       <c r="D10" s="17">
         <f>[7]Main!$D$3</f>
-        <v>73.680000000000007</v>
+        <v>88.28</v>
       </c>
       <c r="E10" s="11">
         <f>[7]Main!$D$5</f>
-        <v>45843.695999999996</v>
+        <v>54362.824000000008</v>
       </c>
       <c r="F10" s="11">
         <f>[7]Main!$D$8</f>
-        <v>-91974</v>
+        <v>-88259</v>
       </c>
       <c r="G10" s="11">
         <f>E10-F10</f>
-        <v>137817.696</v>
+        <v>142621.82400000002</v>
       </c>
       <c r="H10" s="11">
         <f>[7]Model!AO14</f>
@@ -2927,51 +3149,51 @@
       </c>
       <c r="J10" s="11">
         <f>[7]Model!AQ14</f>
-        <v>7978.5110799999984</v>
+        <v>7270.331340000007</v>
       </c>
       <c r="K10" s="11">
         <f>[7]Model!AR14</f>
-        <v>8996.7216356640001</v>
+        <v>9446.2380771600037</v>
       </c>
       <c r="L10" s="11">
         <f>[7]Model!AS14</f>
-        <v>9363.1411170839237</v>
+        <v>10846.165776798605</v>
       </c>
       <c r="M10" s="11">
         <f>[7]Model!AT14</f>
-        <v>9546.9610448283565</v>
+        <v>11071.284089391702</v>
       </c>
       <c r="N10" s="12">
-        <f t="shared" si="3"/>
-        <v>12.207058990256865</v>
+        <f t="shared" si="9"/>
+        <v>12.632579627989372</v>
       </c>
       <c r="O10" s="12">
-        <f t="shared" si="3"/>
-        <v>18.905033744855967</v>
+        <f t="shared" si="9"/>
+        <v>19.564036213991773</v>
       </c>
       <c r="P10" s="12">
-        <f t="shared" si="3"/>
-        <v>17.273610905357046</v>
+        <f t="shared" si="9"/>
+        <v>19.616963427144146</v>
       </c>
       <c r="Q10" s="12">
-        <f t="shared" si="3"/>
-        <v>15.318657348880885</v>
+        <f t="shared" si="9"/>
+        <v>15.098266932827405</v>
       </c>
       <c r="R10" s="12">
-        <f t="shared" si="3"/>
-        <v>14.719173221531262</v>
+        <f t="shared" si="9"/>
+        <v>13.149515408024383</v>
       </c>
       <c r="S10" s="12">
-        <f t="shared" si="3"/>
-        <v>14.435766036214909</v>
-      </c>
-      <c r="T10" s="18">
+        <f t="shared" si="9"/>
+        <v>12.882139311794699</v>
+      </c>
+      <c r="T10" s="29">
         <f>[7]Model!$AO$3</f>
         <v>155498</v>
       </c>
-      <c r="U10" s="27">
-        <f t="shared" si="4"/>
-        <v>0.8862988334255103</v>
+      <c r="U10" s="31">
+        <f t="shared" si="10"/>
+        <v>0.91719394461665116</v>
       </c>
       <c r="V10" s="14">
         <f>[7]Model!$AN$18</f>
@@ -2982,35 +3204,35 @@
         <v>9.0372344155388751E-2</v>
       </c>
       <c r="X10" s="14">
-        <f>[7]Model!$AO$19</f>
-        <v>0.19092850068811174</v>
+        <f>[7]Model!$AQ$19</f>
+        <v>0.16677202510748795</v>
       </c>
       <c r="Y10" s="14">
-        <f>[7]Model!$AO$20</f>
-        <v>0.1188568341715006</v>
+        <f>[7]Model!$AQ$20</f>
+        <v>8.3169312663695386E-2</v>
       </c>
       <c r="Z10" s="14">
         <f>[7]Model!$BD$21</f>
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AA10" s="14">
         <f>[7]Model!$BD$27</f>
-        <v>-0.51311441678656355</v>
+        <v>9.5647188673537054E-2</v>
       </c>
       <c r="AB10" s="14" t="str">
         <f>[7]Model!$BD$28</f>
-        <v>Heavily overvalued</v>
+        <v>Fairly valued</v>
       </c>
       <c r="AC10" s="15">
         <v>1916</v>
       </c>
       <c r="AE10" s="16">
         <f>[7]Main!$E$3</f>
-        <v>45771</v>
+        <v>45904</v>
       </c>
       <c r="AF10" s="16">
         <f>[7]Main!$G$3</f>
-        <v>45784</v>
+        <v>45966</v>
       </c>
     </row>
     <row r="11" spans="2:32" x14ac:dyDescent="0.3">
@@ -3020,224 +3242,345 @@
       <c r="C11" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="10">
         <f>[8]Main!$D$3</f>
-        <v>25.53</v>
+        <v>33.54</v>
       </c>
       <c r="E11" s="11">
         <f>[8]Main!$D$5</f>
-        <v>44080.097999999998</v>
+        <v>48593.869999999995</v>
       </c>
       <c r="F11" s="11">
         <f>[8]Main!$D$10</f>
-        <v>-47632.850505777977</v>
+        <v>-38276.555023923451</v>
       </c>
       <c r="G11" s="11">
         <f>[8]Main!$D$11</f>
-        <v>91712.948505777982</v>
-      </c>
-      <c r="N11" s="12"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
-      <c r="T11" s="13"/>
-      <c r="U11" s="13"/>
-      <c r="V11" s="14"/>
-      <c r="W11" s="14"/>
+        <v>86870.425023923453</v>
+      </c>
+      <c r="H11" s="11">
+        <f>[8]Model!H$17</f>
+        <v>5865.9360469034309</v>
+      </c>
+      <c r="I11" s="11">
+        <f>[8]Model!I$17</f>
+        <v>6638.4488173057462</v>
+      </c>
+      <c r="J11" s="11">
+        <f>[8]Model!J$17</f>
+        <v>4895.8762045959938</v>
+      </c>
+      <c r="K11" s="11">
+        <f>[8]Model!K$17</f>
+        <v>5185.0613296044212</v>
+      </c>
+      <c r="L11" s="11">
+        <f>[8]Model!L$17</f>
+        <v>5495.7142404744263</v>
+      </c>
+      <c r="M11" s="11">
+        <f>[8]Model!M$17</f>
+        <v>5493.7143140376029</v>
+      </c>
+      <c r="N11" s="12">
+        <f t="shared" ref="N11" si="12">$G11/H11</f>
+        <v>14.809303123886167</v>
+      </c>
+      <c r="O11" s="12">
+        <f t="shared" ref="O11" si="13">$G11/I11</f>
+        <v>13.085952368490254</v>
+      </c>
+      <c r="P11" s="12">
+        <f t="shared" ref="P11" si="14">$G11/J11</f>
+        <v>17.743591012855681</v>
+      </c>
+      <c r="Q11" s="12">
+        <f t="shared" ref="Q11" si="15">$G11/K11</f>
+        <v>16.75398216177917</v>
+      </c>
+      <c r="R11" s="12">
+        <f t="shared" ref="R11" si="16">$G11/L11</f>
+        <v>15.806939957712252</v>
+      </c>
+      <c r="S11" s="12">
+        <f t="shared" ref="S11" si="17">$G11/M11</f>
+        <v>15.812694300821418</v>
+      </c>
+      <c r="T11" s="13">
+        <f>[8]Model!$J$3</f>
+        <v>146160.57011928028</v>
+      </c>
+      <c r="U11" s="26">
+        <f t="shared" si="10"/>
+        <v>0.5943492485902957</v>
+      </c>
+      <c r="V11" s="14">
+        <f>[8]Model!$J$26</f>
+        <v>6.1675912273269962E-2</v>
+      </c>
+      <c r="W11" s="14">
+        <f>[8]Model!$K$26</f>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="X11" s="14">
+        <f>[8]Model!$K$21</f>
+        <v>0.21</v>
+      </c>
+      <c r="Y11" s="14">
+        <f>[8]Model!$K$22</f>
+        <v>4.7337701119796835E-2</v>
+      </c>
       <c r="Z11" s="14">
-        <f>[8]Model!$R$23</f>
-        <v>0.06</v>
+        <f>[8]Model!$W$26</f>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AA11" s="14">
-        <f>[8]Model!$R$29</f>
-        <v>0.20695593367719556</v>
+        <f>[8]Model!$W$32</f>
+        <v>-0.33736259729222229</v>
       </c>
       <c r="AB11" s="14" t="str">
-        <f>[8]Model!$R$30</f>
-        <v>Slightly undervalued</v>
+        <f>[8]Model!$W$33</f>
+        <v>Overvalued</v>
       </c>
       <c r="AC11" s="15">
         <v>1948</v>
+      </c>
+      <c r="AE11" s="16">
+        <f>[8]Main!$E$3</f>
+        <v>45904</v>
+      </c>
+      <c r="AF11" s="16">
+        <f>[8]Main!$G$3</f>
+        <v>45966</v>
       </c>
     </row>
     <row r="12" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B12" s="21" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D12" s="24">
         <f>[9]Main!$D$3</f>
-        <v>46.72</v>
+        <v>41.45</v>
       </c>
       <c r="E12" s="11">
         <f>[9]Main!$D$5</f>
-        <v>42561.919999999998</v>
+        <v>37760.950000000004</v>
       </c>
       <c r="F12" s="11">
         <f>[9]Main!$D$8</f>
-        <v>-5029</v>
+        <v>-2528</v>
       </c>
       <c r="G12" s="11">
         <f>[9]Main!$D$9</f>
-        <v>47590.92</v>
+        <v>40288.950000000004</v>
       </c>
       <c r="H12" s="11">
-        <f>[9]Model!N$19</f>
+        <f>[9]Model!V$49</f>
         <v>5156</v>
       </c>
       <c r="I12" s="11">
-        <f>[9]Model!O$19</f>
-        <v>3596</v>
+        <f>[9]Model!W$49</f>
+        <v>3593</v>
+      </c>
+      <c r="J12" s="11">
+        <f>[9]Model!X$49</f>
+        <v>2058.3172399999958</v>
+      </c>
+      <c r="K12" s="11">
+        <f>[9]Model!Y$49</f>
+        <v>3097.2513473999998</v>
+      </c>
+      <c r="L12" s="11">
+        <f>[9]Model!Z$49</f>
+        <v>3707.8589376360001</v>
+      </c>
+      <c r="M12" s="11">
+        <f>[9]Model!AA$49</f>
+        <v>4061.902063665601</v>
       </c>
       <c r="N12" s="12">
-        <f t="shared" ref="N12" si="6">$G12/H12</f>
-        <v>9.2302017067494173</v>
+        <f t="shared" ref="N12" si="18">$G12/H12</f>
+        <v>7.8139934057408853</v>
       </c>
       <c r="O12" s="12">
-        <f t="shared" ref="O12" si="7">$G12/I12</f>
-        <v>13.23440489432703</v>
-      </c>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
-      <c r="T12" s="25">
-        <f>[9]Model!$N$3</f>
+        <f t="shared" ref="O12" si="19">$G12/I12</f>
+        <v>11.213178402449207</v>
+      </c>
+      <c r="P12" s="12">
+        <f t="shared" ref="P12" si="20">$G12/J12</f>
+        <v>19.573731987009005</v>
+      </c>
+      <c r="Q12" s="12">
+        <f t="shared" ref="Q12" si="21">$G12/K12</f>
+        <v>13.007969157498543</v>
+      </c>
+      <c r="R12" s="12">
+        <f t="shared" ref="R12" si="22">$G12/L12</f>
+        <v>10.865825986812437</v>
+      </c>
+      <c r="S12" s="12">
+        <f t="shared" ref="S12" si="23">$G12/M12</f>
+        <v>9.9187398830689339</v>
+      </c>
+      <c r="T12" s="30">
+        <f>[9]Model!$V$30</f>
         <v>40530</v>
       </c>
-      <c r="U12" s="27">
-        <f t="shared" ref="U12:U13" si="8">G12/T12</f>
-        <v>1.1742146558105107</v>
-      </c>
-      <c r="V12" s="14"/>
-      <c r="W12" s="14"/>
+      <c r="U12" s="31">
+        <f t="shared" ref="U12:U13" si="24">G12/T12</f>
+        <v>0.99405255366395273</v>
+      </c>
+      <c r="V12" s="14">
+        <f>[9]Model!$W$53</f>
+        <v>-1.1028867505551432E-2</v>
+      </c>
+      <c r="W12" s="14">
+        <f>[9]Model!$X$53</f>
+        <v>-6.0456303170920433E-2</v>
+      </c>
+      <c r="X12" s="14">
+        <f>[9]Model!$X$54</f>
+        <v>0.21190611563067488</v>
+      </c>
+      <c r="Y12" s="14">
+        <f>[9]Model!$X$57</f>
+        <v>7.9327525715133795E-2</v>
+      </c>
+      <c r="Z12" s="14">
+        <f>[9]Model!$AK$56</f>
+        <v>0.08</v>
+      </c>
+      <c r="AA12" s="14">
+        <f>[9]Model!$AK$62</f>
+        <v>0.32757142189307098</v>
+      </c>
+      <c r="AB12" s="14" t="str">
+        <f>[9]Model!$AK$63</f>
+        <v>Undervalued</v>
+      </c>
+      <c r="AC12" s="15">
+        <v>1931</v>
+      </c>
       <c r="AE12" s="16">
         <f>[9]Main!$E$3</f>
-        <v>45771</v>
+        <v>45923</v>
       </c>
       <c r="AF12" s="16">
         <f>[9]Main!$G$3</f>
-        <v>45776</v>
+        <v>45954</v>
       </c>
     </row>
     <row r="13" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B13" s="26" t="s">
-        <v>65</v>
+      <c r="B13" s="25" t="s">
+        <v>60</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D13" s="22">
         <f>[10]Main!$D$3</f>
-        <v>8</v>
+        <v>7.5670000000000002</v>
       </c>
       <c r="E13" s="11">
         <f>[10]Main!$D$5</f>
-        <v>30100.799999999999</v>
+        <v>21812.6342</v>
       </c>
       <c r="F13" s="11">
         <f>[10]Main!$D$8</f>
-        <v>-3127</v>
+        <v>-10139</v>
       </c>
       <c r="G13" s="11">
         <f>[10]Main!$D$9</f>
-        <v>33227.800000000003</v>
+        <v>31951.6342</v>
       </c>
       <c r="H13" s="11">
-        <f>[10]Model!Q$17</f>
+        <f>[10]Model!Q$24</f>
         <v>18596</v>
       </c>
       <c r="I13" s="11">
-        <f>[10]Model!R$17</f>
+        <f>[10]Model!R$24</f>
         <v>5473</v>
       </c>
       <c r="J13" s="11">
-        <f>[10]Model!S$17</f>
-        <v>-121.04400000000184</v>
+        <f>[10]Model!S$24</f>
+        <v>-3955.4684000000334</v>
       </c>
       <c r="K13" s="11">
-        <f>[10]Model!T$17</f>
-        <v>2322.7907304000009</v>
+        <f>[10]Model!T$24</f>
+        <v>-980.07988364999983</v>
       </c>
       <c r="L13" s="11">
-        <f>[10]Model!U$17</f>
-        <v>4719.6040671360006</v>
+        <f>[10]Model!U$24</f>
+        <v>1842.0949888019975</v>
       </c>
       <c r="M13" s="11">
-        <f>[10]Model!V$17</f>
-        <v>5964.6729261672017</v>
+        <f>[10]Model!V$24</f>
+        <v>5262.873720354808</v>
       </c>
       <c r="N13" s="12">
         <f>$G13/H13</f>
-        <v>1.7868251236825126</v>
+        <v>1.7181993009249301</v>
       </c>
       <c r="O13" s="12">
         <f>$G13/I13</f>
-        <v>6.0712223643340035</v>
-      </c>
-      <c r="P13" s="12">
-        <f t="shared" ref="P13:S13" si="9">$G13/J13</f>
-        <v>-274.51009550245777</v>
-      </c>
-      <c r="Q13" s="12">
-        <f t="shared" si="9"/>
-        <v>14.305119942629503</v>
-      </c>
+        <v>5.8380475424812719</v>
+      </c>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
       <c r="R13" s="12">
-        <f t="shared" si="9"/>
-        <v>7.0403787112938145</v>
+        <f t="shared" ref="R13:S13" si="25">$G13/L13</f>
+        <v>17.345269594799603</v>
       </c>
       <c r="S13" s="12">
-        <f t="shared" si="9"/>
-        <v>5.5707664797894676</v>
-      </c>
-      <c r="T13" s="13">
-        <f>[10]Model!$Q$3</f>
+        <f t="shared" si="25"/>
+        <v>6.0711382977750628</v>
+      </c>
+      <c r="T13" s="28">
+        <f>[10]Model!$Q$10</f>
         <v>189544</v>
       </c>
-      <c r="U13" s="27">
-        <f t="shared" si="8"/>
-        <v>0.17530388722407464</v>
+      <c r="U13" s="31">
+        <f t="shared" si="24"/>
+        <v>0.16857106634871058</v>
       </c>
       <c r="V13" s="14"/>
       <c r="W13" s="14">
-        <f>[10]Model!$Q$21</f>
+        <f>[10]Model!$Q$35</f>
         <v>5.5414495077731774E-2</v>
       </c>
       <c r="X13" s="14">
-        <f>[10]Model!$Q$22</f>
-        <v>0.20124087283163802</v>
+        <f>[10]Model!$S$36</f>
+        <v>8.5394651372724173E-2</v>
       </c>
       <c r="Y13" s="14">
-        <f>[10]Model!$Q$25</f>
-        <v>0.11805174524121048</v>
+        <f>[10]Model!$S$39</f>
+        <v>-3.1254943975238522E-2</v>
       </c>
       <c r="Z13" s="14">
-        <f>[10]Model!$AF$24</f>
-        <v>0.08</v>
+        <f>[10]Model!$AF$38</f>
+        <v>0.09</v>
       </c>
       <c r="AA13" s="14">
-        <f>[10]Model!$AF$30</f>
-        <v>1.3973121928006629</v>
+        <f>[10]Model!$AF$44</f>
+        <v>1.6974869917057078</v>
       </c>
       <c r="AB13" s="14" t="str">
-        <f>[10]Model!$AF$31</f>
+        <f>[10]Model!$AF$45</f>
         <v>Heavily undervalued</v>
       </c>
       <c r="AC13" s="15" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="AE13" s="16">
         <f>[10]Main!$E$3</f>
-        <v>45771</v>
+        <v>45868</v>
       </c>
       <c r="AF13" s="16">
         <f>[10]Main!$G$3</f>
-        <v>45777</v>
+        <v>45960</v>
       </c>
     </row>
     <row r="14" spans="2:32" x14ac:dyDescent="0.3">
@@ -3269,8 +3612,8 @@
       <c r="Q14" s="12"/>
       <c r="R14" s="12"/>
       <c r="S14" s="12"/>
-      <c r="T14" s="18"/>
-      <c r="U14" s="18"/>
+      <c r="T14" s="29"/>
+      <c r="U14" s="29"/>
       <c r="V14" s="14"/>
       <c r="W14" s="14"/>
       <c r="Z14" s="14">
@@ -3299,18 +3642,18 @@
     </row>
     <row r="15" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B15" s="9" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D15" s="10">
         <f>[12]Main!$D$3</f>
-        <v>11.96</v>
+        <v>13.57</v>
       </c>
       <c r="E15" s="11">
         <f>[12]Main!$D$5</f>
-        <v>12653.68</v>
+        <v>16465.838000000003</v>
       </c>
       <c r="F15" s="11">
         <f>[12]Main!$D$8</f>
@@ -3318,7 +3661,7 @@
       </c>
       <c r="G15" s="11">
         <f>[12]Main!$D$9</f>
-        <v>9394.68</v>
+        <v>13206.838000000003</v>
       </c>
       <c r="H15" s="11">
         <f>[12]Model!X$21</f>
@@ -3330,54 +3673,54 @@
       </c>
       <c r="J15" s="11">
         <f>[12]Model!Z$21</f>
-        <v>-2737.1781026800018</v>
+        <v>-2883.1596</v>
       </c>
       <c r="K15" s="11">
         <f>[12]Model!AA$21</f>
-        <v>-2431.7268265104008</v>
+        <v>-2176.9613879999993</v>
       </c>
       <c r="L15" s="11">
         <f>[12]Model!AB$21</f>
-        <v>-2099.6875420206088</v>
+        <v>-1518.9675790080003</v>
       </c>
       <c r="M15" s="11">
         <f>[12]Model!AC$21</f>
-        <v>-1692.1326230002155</v>
+        <v>-1276.1137779020798</v>
       </c>
       <c r="T15" s="13">
-        <f>[12]Model!$X$5</f>
-        <v>4434</v>
-      </c>
-      <c r="U15" s="27">
-        <f t="shared" ref="U15:U17" si="10">G15/T15</f>
-        <v>2.1187821380243572</v>
+        <f>[12]Model!$Z$5</f>
+        <v>5583</v>
+      </c>
+      <c r="U15" s="26">
+        <f t="shared" ref="U15:U17" si="26">G15/T15</f>
+        <v>2.3655450474655209</v>
       </c>
       <c r="V15" s="14">
-        <f>[12]Model!$W$25</f>
+        <f>[12]Model!$W$27</f>
         <v>29.145454545454545</v>
       </c>
       <c r="W15" s="14">
-        <f>[12]Model!$X$25</f>
+        <f>[12]Model!$X$27</f>
         <v>1.6743063932448732</v>
       </c>
       <c r="X15" s="14">
-        <f>[12]Model!$X$26</f>
-        <v>-0.45782589084348219</v>
+        <f>[12]Model!$Z$30</f>
+        <v>0.10388679921189324</v>
       </c>
       <c r="Y15" s="14">
-        <f>[12]Model!$Y$26</f>
-        <v>-0.2414486921529175</v>
+        <f>[12]Model!$Z$33</f>
+        <v>-0.53904703564391909</v>
       </c>
       <c r="Z15" s="14">
-        <f>[12]Model!$AN$27</f>
+        <f>[12]Model!$AN$31</f>
         <v>0.09</v>
       </c>
       <c r="AA15" s="14">
-        <f>[12]Model!$AN$78</f>
-        <v>-1.0978041506643392</v>
+        <f>[12]Model!$AN$82</f>
+        <v>-0.77098230893300101</v>
       </c>
       <c r="AB15" s="14" t="str">
-        <f>[12]Model!$AN$34</f>
+        <f>[12]Model!$AN$38</f>
         <v>Heavily overvalued</v>
       </c>
       <c r="AC15" s="15">
@@ -3385,103 +3728,106 @@
       </c>
       <c r="AE15" s="16">
         <f>[12]Main!$E$3</f>
-        <v>45713</v>
+        <v>45899</v>
       </c>
       <c r="AF15" s="16">
         <f>[12]Main!$G$3</f>
-        <v>45790</v>
+        <v>45966</v>
       </c>
     </row>
     <row r="16" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B16" s="21" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D16" s="10">
         <f>[13]Main!$D$3</f>
-        <v>2.46</v>
+        <v>1.98</v>
       </c>
       <c r="E16" s="11">
         <f>[13]Main!$D$5</f>
-        <v>7457.49</v>
+        <v>6083.55</v>
       </c>
       <c r="F16" s="11">
         <f>[13]Main!$D$8</f>
-        <v>2028.8</v>
+        <v>1563.6</v>
       </c>
       <c r="G16" s="11">
         <f>[13]Main!$D$9</f>
-        <v>5428.69</v>
+        <v>4519.9500000000007</v>
       </c>
       <c r="H16" s="11">
-        <f>[13]Model!AB$14</f>
+        <f>[13]Model!AB$17</f>
         <v>-2828.3</v>
       </c>
       <c r="I16" s="11">
-        <f>[13]Model!AC$14</f>
+        <f>[13]Model!AC$17</f>
         <v>-2714.0000000000005</v>
       </c>
       <c r="J16" s="11">
-        <f>[13]Model!AD$14</f>
-        <v>-2534.33</v>
+        <f>[13]Model!AD$17</f>
+        <v>-1573.4800000000002</v>
       </c>
       <c r="K16" s="11">
-        <f>[13]Model!AE$14</f>
-        <v>-2333.4748500000001</v>
+        <f>[13]Model!AE$17</f>
+        <v>-1338.9207800000001</v>
       </c>
       <c r="L16" s="11">
-        <f>[13]Model!AF$14</f>
-        <v>-1943.7248985000001</v>
+        <f>[13]Model!AF$17</f>
+        <v>-909.73493530000019</v>
       </c>
       <c r="M16" s="11">
-        <f>[13]Model!AG$14</f>
-        <v>-1535.5301804850001</v>
+        <f>[13]Model!AG$17</f>
+        <v>-460.13275752800018</v>
       </c>
       <c r="T16" s="13">
-        <f>[13]Model!$AB$3</f>
-        <v>595.29999999999995</v>
-      </c>
-      <c r="U16" s="27">
-        <f t="shared" si="10"/>
-        <v>9.119250797917017</v>
+        <f>[13]Model!$AD$6</f>
+        <v>1191.3249999999998</v>
+      </c>
+      <c r="U16" s="26">
+        <f t="shared" si="26"/>
+        <v>3.7940528403248495</v>
       </c>
       <c r="V16" s="14">
-        <f>[13]Model!$AA$18</f>
+        <f>[13]Model!$AA$26</f>
         <v>21.44280442804428</v>
       </c>
       <c r="W16" s="14">
-        <f>[13]Model!$AB$18</f>
+        <f>[13]Model!$AB$26</f>
         <v>-2.1210128247287185E-2</v>
       </c>
       <c r="X16" s="14">
-        <f>[13]Model!$AB$19</f>
-        <v>-2.2523097597849824</v>
+        <f>[13]Model!$AD$27</f>
+        <v>-0.6</v>
       </c>
       <c r="Y16" s="14">
-        <f>[13]Model!$AB$22</f>
-        <v>-5.2066185116747858</v>
+        <f>[13]Model!$AD$31</f>
+        <v>-2.3225232409292178</v>
       </c>
       <c r="Z16" s="14">
-        <f>[13]Model!$AQ$20</f>
-        <v>0.1</v>
+        <f>[13]Model!$AQ$28</f>
+        <v>0.09</v>
       </c>
       <c r="AA16" s="14">
-        <f>[13]Model!$AQ$26</f>
-        <v>-1.7560259481433871</v>
+        <f>[13]Model!$AQ$34</f>
+        <v>-0.1348443553182711</v>
       </c>
       <c r="AB16" s="14" t="str">
-        <f>[13]Model!$AQ$27</f>
-        <v>Heavily overvalued</v>
+        <f>[13]Model!$AQ$35</f>
+        <v>Slightly overvalued</v>
+      </c>
+      <c r="AC16" s="15">
+        <v>2007</v>
       </c>
       <c r="AE16" s="16">
         <f>[13]Main!$E$3</f>
-        <v>45771</v>
+        <v>45889</v>
       </c>
       <c r="AF16" s="16">
         <f>[13]Main!$G$3</f>
-        <v>45783</v>
+        <v>45972</v>
       </c>
     </row>
     <row r="17" spans="2:32" x14ac:dyDescent="0.3">
@@ -3493,102 +3839,90 @@
       </c>
       <c r="D17" s="19">
         <f>[14]Main!$D$3</f>
-        <v>1.0980000000000001</v>
+        <v>0.71850000000000003</v>
       </c>
       <c r="E17" s="11">
         <f>[14]Main!$D$5</f>
-        <v>905.85</v>
+        <v>686.52674999999999</v>
       </c>
       <c r="F17" s="11">
         <f>[14]Main!$D$8</f>
-        <v>-974.2</v>
+        <v>-1169.8</v>
       </c>
       <c r="G17" s="11">
         <f>E17-F17</f>
-        <v>1880.0500000000002</v>
+        <v>1856.3267499999999</v>
       </c>
       <c r="H17" s="11">
-        <f>[14]Model!AH15</f>
+        <f>[14]Model!AL15</f>
         <v>-228.10000000000014</v>
       </c>
       <c r="I17" s="11">
-        <f>[14]Model!AI15</f>
-        <v>-239.64460000000003</v>
+        <f>[14]Model!AM15</f>
+        <v>-323.49999999999989</v>
       </c>
       <c r="J17" s="11">
-        <f>[14]Model!AJ15</f>
-        <v>-137.36318280000003</v>
+        <f>[14]Model!AN15</f>
+        <v>-169.45059199999997</v>
       </c>
       <c r="K17" s="11">
-        <f>[14]Model!AK15</f>
-        <v>-45.433853162400069</v>
+        <f>[14]Model!AO15</f>
+        <v>-24.605004735999863</v>
       </c>
       <c r="L17" s="11">
-        <f>[14]Model!AL15</f>
-        <v>28.41758343130066</v>
+        <f>[14]Model!AP15</f>
+        <v>83.85838662611188</v>
       </c>
       <c r="M17" s="11">
-        <f>[14]Model!AM15</f>
-        <v>79.191899431941238</v>
-      </c>
-      <c r="N17" s="12">
-        <f t="shared" ref="N17:S17" si="11">$G17/H17</f>
-        <v>-8.2422183252959194</v>
-      </c>
-      <c r="O17" s="12">
-        <f t="shared" si="11"/>
-        <v>-7.8451590396779229</v>
-      </c>
-      <c r="P17" s="12">
-        <f t="shared" si="11"/>
-        <v>-13.686709653032295</v>
-      </c>
-      <c r="Q17" s="12">
-        <f t="shared" si="11"/>
-        <v>-41.379937406583046</v>
-      </c>
+        <f>[14]Model!AQ15</f>
+        <v>165.4102204171208</v>
+      </c>
+      <c r="N17" s="12"/>
+      <c r="O17" s="12"/>
+      <c r="P17" s="12"/>
+      <c r="Q17" s="12"/>
       <c r="R17" s="12">
-        <f t="shared" si="11"/>
-        <v>66.15798294548901</v>
+        <f t="shared" ref="R17:S17" si="27">$G17/L17</f>
+        <v>22.136447225923323</v>
       </c>
       <c r="S17" s="12">
-        <f t="shared" si="11"/>
-        <v>23.740433219634347</v>
+        <f t="shared" si="27"/>
+        <v>11.222563789098613</v>
       </c>
       <c r="T17" s="20">
-        <f>[14]Model!$AH$3</f>
-        <v>1632.8</v>
-      </c>
-      <c r="U17" s="27">
-        <f t="shared" si="10"/>
-        <v>1.1514269965703088</v>
+        <f>[14]Model!$AN$3</f>
+        <v>1631.4170000000001</v>
+      </c>
+      <c r="U17" s="26">
+        <f t="shared" si="26"/>
+        <v>1.1378615951654296</v>
       </c>
       <c r="V17" s="14">
-        <f>[14]Model!$AG$19</f>
+        <f>[14]Model!$AK$19</f>
         <v>0.26129827444535758</v>
       </c>
       <c r="W17" s="14">
-        <f>[14]Model!$AH$19</f>
+        <f>[14]Model!$AL$19</f>
         <v>0.18190372783206654</v>
       </c>
       <c r="X17" s="14">
-        <f>[14]Model!$AH$20</f>
-        <v>0.3914747672709456</v>
+        <f>[14]Model!$AN$20</f>
+        <v>0.37</v>
       </c>
       <c r="Y17" s="14">
-        <f>[14]Model!$AH$21</f>
-        <v>-6.8103870651641418E-2</v>
+        <f>[14]Model!$AN$21</f>
+        <v>-1.5595791879084222E-2</v>
       </c>
       <c r="Z17" s="14">
-        <f>[14]Model!$AW$19</f>
-        <v>0.08</v>
+        <f>[14]Model!$BA$19</f>
+        <v>0.1</v>
       </c>
       <c r="AA17" s="14">
-        <f>[14]Model!$AW$25</f>
-        <v>-0.45006922200548305</v>
+        <f>[14]Model!$BA$25</f>
+        <v>-0.3508624801279675</v>
       </c>
       <c r="AB17" s="14" t="str">
-        <f>[14]Model!$AW$26</f>
+        <f>[14]Model!$BA$26</f>
         <v>Overvalued</v>
       </c>
       <c r="AC17" s="15">
@@ -3596,11 +3930,11 @@
       </c>
       <c r="AE17" s="16">
         <f>[14]Main!$E$3</f>
-        <v>45635</v>
+        <v>45869</v>
       </c>
       <c r="AF17" s="16">
         <f>[14]Main!$G$3</f>
-        <v>45715</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="18" spans="2:32" x14ac:dyDescent="0.3">
@@ -3648,20 +3982,20 @@
     </row>
     <row r="26" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B27" s="9" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B28" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/Models (Automotive).xlsx
+++ b/Financial Analysis/Models (Automotive).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E6B13EA-5DB6-4C62-A6C1-F162B33F00D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E013CB36-0546-439D-B637-420CD70FB231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{44A3A52B-B984-4465-AC96-672BE039DB0B}"/>
   </bookViews>

--- a/Financial Analysis/Models (Automotive).xlsx
+++ b/Financial Analysis/Models (Automotive).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E013CB36-0546-439D-B637-420CD70FB231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{150F7A1B-0B5B-4CDF-A0AE-1B76F1AF5F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{44A3A52B-B984-4465-AC96-672BE039DB0B}"/>
   </bookViews>
@@ -620,10 +620,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>7.5670000000000002</v>
+            <v>9.4710000000000001</v>
           </cell>
           <cell r="E3">
-            <v>45868</v>
+            <v>45937</v>
           </cell>
           <cell r="G3">
             <v>45960</v>
@@ -631,7 +631,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>21812.6342</v>
+            <v>27301.104599999999</v>
           </cell>
         </row>
         <row r="8">
@@ -641,7 +641,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>31951.6342</v>
+            <v>37440.104599999999</v>
           </cell>
         </row>
       </sheetData>
@@ -693,7 +693,7 @@
         </row>
         <row r="44">
           <cell r="AF44">
-            <v>1.6974869917057078</v>
+            <v>1.1551984020945087</v>
           </cell>
         </row>
         <row r="45">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="R3" s="6">
         <f t="shared" si="0"/>
-        <v>15.824896923557986</v>
+        <v>16.013126375057436</v>
       </c>
       <c r="S3" s="6">
         <f t="shared" si="0"/>
@@ -3482,11 +3482,11 @@
       </c>
       <c r="D13" s="22">
         <f>[10]Main!$D$3</f>
-        <v>7.5670000000000002</v>
+        <v>9.4710000000000001</v>
       </c>
       <c r="E13" s="11">
         <f>[10]Main!$D$5</f>
-        <v>21812.6342</v>
+        <v>27301.104599999999</v>
       </c>
       <c r="F13" s="11">
         <f>[10]Main!$D$8</f>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="G13" s="11">
         <f>[10]Main!$D$9</f>
-        <v>31951.6342</v>
+        <v>37440.104599999999</v>
       </c>
       <c r="H13" s="11">
         <f>[10]Model!Q$24</f>
@@ -3522,21 +3522,21 @@
       </c>
       <c r="N13" s="12">
         <f>$G13/H13</f>
-        <v>1.7181993009249301</v>
+        <v>2.0133418261991824</v>
       </c>
       <c r="O13" s="12">
         <f>$G13/I13</f>
-        <v>5.8380475424812719</v>
+        <v>6.8408742188927461</v>
       </c>
       <c r="P13" s="12"/>
       <c r="Q13" s="12"/>
       <c r="R13" s="12">
         <f t="shared" ref="R13:S13" si="25">$G13/L13</f>
-        <v>17.345269594799603</v>
+        <v>20.324741572826866</v>
       </c>
       <c r="S13" s="12">
         <f t="shared" si="25"/>
-        <v>6.0711382977750628</v>
+        <v>7.1140039813601863</v>
       </c>
       <c r="T13" s="28">
         <f>[10]Model!$Q$10</f>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="U13" s="31">
         <f t="shared" si="24"/>
-        <v>0.16857106634871058</v>
+        <v>0.19752724749926137</v>
       </c>
       <c r="V13" s="14"/>
       <c r="W13" s="14">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="AA13" s="14">
         <f>[10]Model!$AF$44</f>
-        <v>1.6974869917057078</v>
+        <v>1.1551984020945087</v>
       </c>
       <c r="AB13" s="14" t="str">
         <f>[10]Model!$AF$45</f>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="AE13" s="16">
         <f>[10]Main!$E$3</f>
-        <v>45868</v>
+        <v>45937</v>
       </c>
       <c r="AF13" s="16">
         <f>[10]Main!$G$3</f>

--- a/Financial Analysis/Models (Automotive).xlsx
+++ b/Financial Analysis/Models (Automotive).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{150F7A1B-0B5B-4CDF-A0AE-1B76F1AF5F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76BED8FC-37D0-49A7-90F7-D63A0AB7A062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{44A3A52B-B984-4465-AC96-672BE039DB0B}"/>
   </bookViews>
@@ -359,7 +359,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -375,6 +375,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -407,7 +413,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -489,6 +495,7 @@
     <xf numFmtId="9" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -521,30 +528,30 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>312.60000000000002</v>
+            <v>433.72</v>
           </cell>
           <cell r="E3">
-            <v>45862</v>
+            <v>45956</v>
           </cell>
           <cell r="G3">
-            <v>45945</v>
+            <v>46050</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>1007509.8</v>
+            <v>1442465.9760000003</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>29562</v>
+            <v>33945</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="6">
           <cell r="AW6">
-            <v>64034.32</v>
+            <v>73266.949999999983</v>
           </cell>
         </row>
         <row r="27">
@@ -555,16 +562,16 @@
             <v>7091</v>
           </cell>
           <cell r="AW27">
-            <v>3108.4869984000024</v>
+            <v>4071.1940119999881</v>
           </cell>
           <cell r="AX27">
-            <v>6756.6394432400202</v>
+            <v>7282.7460136000045</v>
           </cell>
           <cell r="AY27">
-            <v>7545.3029727164021</v>
+            <v>8046.1759089979996</v>
           </cell>
           <cell r="AZ27">
-            <v>8985.0711792893107</v>
+            <v>9752.7441125739933</v>
           </cell>
         </row>
         <row r="31">
@@ -582,7 +589,7 @@
         </row>
         <row r="37">
           <cell r="BJ37">
-            <v>-0.69705744731799135</v>
+            <v>-0.79546859376188694</v>
           </cell>
         </row>
         <row r="38">
@@ -782,10 +789,10 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>13.57</v>
+            <v>12.68</v>
           </cell>
           <cell r="E3">
-            <v>45899</v>
+            <v>45965</v>
           </cell>
           <cell r="G3">
             <v>45966</v>
@@ -793,7 +800,7 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>16465.838000000003</v>
+            <v>15385.912</v>
           </cell>
         </row>
         <row r="8">
@@ -803,7 +810,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>13206.838000000003</v>
+            <v>12126.912</v>
           </cell>
         </row>
       </sheetData>
@@ -863,7 +870,7 @@
         </row>
         <row r="82">
           <cell r="AN82">
-            <v>-0.77098230893300101</v>
+            <v>-0.75490772336126366</v>
           </cell>
         </row>
       </sheetData>
@@ -1287,18 +1294,18 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>52.41</v>
+            <v>69.5</v>
           </cell>
           <cell r="E3">
-            <v>45863</v>
+            <v>45957</v>
           </cell>
           <cell r="G3">
-            <v>45951</v>
+            <v>46049</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>49899.561000000002</v>
+            <v>64836.549999999996</v>
           </cell>
         </row>
         <row r="8">
@@ -1308,7 +1315,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>155088.56099999999</v>
+            <v>170025.55</v>
           </cell>
         </row>
       </sheetData>
@@ -1363,7 +1370,7 @@
         </row>
         <row r="31">
           <cell r="BD31">
-            <v>-0.1271295548656699</v>
+            <v>-0.32822070233413636</v>
           </cell>
         </row>
         <row r="32">
@@ -1391,18 +1398,18 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>10.67</v>
+            <v>13.76</v>
           </cell>
           <cell r="E3">
-            <v>45869</v>
+            <v>45957</v>
           </cell>
           <cell r="G3">
-            <v>45952</v>
+            <v>46063</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>42466.6</v>
+            <v>54709.760000000002</v>
           </cell>
         </row>
         <row r="8">
@@ -1425,16 +1432,16 @@
             <v>5879</v>
           </cell>
           <cell r="AQ13">
-            <v>1239.4415999999778</v>
+            <v>3627.3646399999848</v>
           </cell>
           <cell r="AR13">
-            <v>4261.1494255000007</v>
+            <v>4391.6180773600036</v>
           </cell>
           <cell r="AS13">
-            <v>6642.8283350600059</v>
+            <v>7062.2854109840036</v>
           </cell>
           <cell r="AT13">
-            <v>7185.6523113568019</v>
+            <v>7624.8583346045261</v>
           </cell>
         </row>
         <row r="17">
@@ -1462,7 +1469,7 @@
         </row>
         <row r="26">
           <cell r="BD26">
-            <v>-0.61304644993749069</v>
+            <v>-0.51829813263956948</v>
           </cell>
         </row>
         <row r="27">
@@ -1792,18 +1799,18 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>41.45</v>
+            <v>48.41</v>
           </cell>
           <cell r="E3">
-            <v>45923</v>
+            <v>45957</v>
           </cell>
           <cell r="G3">
-            <v>45954</v>
+            <v>46098</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>37760.950000000004</v>
+            <v>44101.509999999995</v>
           </cell>
         </row>
         <row r="8">
@@ -1813,7 +1820,7 @@
         </row>
         <row r="9">
           <cell r="D9">
-            <v>40288.950000000004</v>
+            <v>46629.509999999995</v>
           </cell>
         </row>
       </sheetData>
@@ -1831,16 +1838,16 @@
             <v>3593</v>
           </cell>
           <cell r="X49">
-            <v>2058.3172399999958</v>
+            <v>187.69510000000761</v>
           </cell>
           <cell r="Y49">
-            <v>3097.2513473999998</v>
+            <v>3128.7290790000015</v>
           </cell>
           <cell r="Z49">
-            <v>3707.8589376360001</v>
+            <v>3741.0556692600021</v>
           </cell>
           <cell r="AA49">
-            <v>4061.902063665601</v>
+            <v>4096.4204070720016</v>
           </cell>
         </row>
         <row r="53">
@@ -1848,12 +1855,12 @@
             <v>-1.1028867505551432E-2</v>
           </cell>
           <cell r="X53">
-            <v>-6.0456303170920433E-2</v>
+            <v>-5.8914003442856022E-2</v>
           </cell>
         </row>
         <row r="54">
           <cell r="X54">
-            <v>0.21190611563067488</v>
+            <v>0.12996900975702236</v>
           </cell>
         </row>
         <row r="56">
@@ -1863,17 +1870,17 @@
         </row>
         <row r="57">
           <cell r="X57">
-            <v>7.9327525715133795E-2</v>
+            <v>4.5595422245376356E-3</v>
           </cell>
         </row>
         <row r="62">
           <cell r="AK62">
-            <v>0.32757142189307098</v>
+            <v>0.10692975287950546</v>
           </cell>
         </row>
         <row r="63">
           <cell r="AK63" t="str">
-            <v>Undervalued</v>
+            <v>Fairly valued</v>
           </cell>
         </row>
       </sheetData>
@@ -2351,24 +2358,24 @@
       </c>
       <c r="P3" s="6">
         <f t="shared" si="0"/>
-        <v>19.635704216861978</v>
+        <v>21.134509026188805</v>
       </c>
       <c r="Q3" s="6">
         <f t="shared" si="0"/>
-        <v>15.513504835381363</v>
+        <v>15.985060049740932</v>
       </c>
       <c r="R3" s="6">
         <f t="shared" si="0"/>
-        <v>16.013126375057436</v>
+        <v>16.47293837543743</v>
       </c>
       <c r="S3" s="6">
         <f t="shared" si="0"/>
-        <v>13.25662183271748</v>
+        <v>13.705835387570835</v>
       </c>
       <c r="T3" s="4"/>
       <c r="U3" s="27">
         <f t="shared" si="0"/>
-        <v>0.96851754398012357</v>
+        <v>1.0405324209773694</v>
       </c>
       <c r="V3" s="7">
         <f t="shared" ref="V3:AA3" si="1">TRIMMEAN(V4:V1048576,80%)</f>
@@ -2380,11 +2387,11 @@
       </c>
       <c r="X3" s="7">
         <f t="shared" si="1"/>
-        <v>0.1831298971399147</v>
+        <v>0.17560646577683295</v>
       </c>
       <c r="Y3" s="7">
         <f t="shared" si="1"/>
-        <v>5.6855532694324286E-2</v>
+        <v>4.4141096704330883E-2</v>
       </c>
       <c r="Z3" s="7">
         <f t="shared" si="1"/>
@@ -2392,7 +2399,7 @@
       </c>
       <c r="AA3" s="7">
         <f t="shared" si="1"/>
-        <v>-0.19797272187116063</v>
+        <v>-0.24824550873827725</v>
       </c>
       <c r="AB3" s="8" t="str">
         <f>INDEX(AB4:AB17,MODE(MATCH(AB4:AB17,AB4:AB17,0)))</f>
@@ -2411,19 +2418,19 @@
       </c>
       <c r="D4" s="10">
         <f>[1]Main!$D$3</f>
-        <v>312.60000000000002</v>
+        <v>433.72</v>
       </c>
       <c r="E4" s="11">
         <f>[1]Main!$D$5</f>
-        <v>1007509.8</v>
+        <v>1442465.9760000003</v>
       </c>
       <c r="F4" s="11">
         <f>[1]Main!$D$8</f>
-        <v>29562</v>
+        <v>33945</v>
       </c>
       <c r="G4" s="11">
         <f>E4-F4</f>
-        <v>977947.8</v>
+        <v>1408520.9760000003</v>
       </c>
       <c r="H4" s="11">
         <f>[1]Model!AU$27</f>
@@ -2435,51 +2442,51 @@
       </c>
       <c r="J4" s="11">
         <f>[1]Model!AW$27</f>
-        <v>3108.4869984000024</v>
+        <v>4071.1940119999881</v>
       </c>
       <c r="K4" s="11">
         <f>[1]Model!AX$27</f>
-        <v>6756.6394432400202</v>
+        <v>7282.7460136000045</v>
       </c>
       <c r="L4" s="11">
         <f>[1]Model!AY$27</f>
-        <v>7545.3029727164021</v>
+        <v>8046.1759089979996</v>
       </c>
       <c r="M4" s="11">
         <f>[1]Model!AZ$27</f>
-        <v>8985.0711792893107</v>
+        <v>9752.7441125739933</v>
       </c>
       <c r="N4" s="12">
         <f t="shared" ref="N4:S4" si="2">$G4/H4</f>
-        <v>65.209561912382483</v>
+        <v>93.920182436487309</v>
       </c>
       <c r="O4" s="12">
         <f t="shared" si="2"/>
-        <v>137.91394725708645</v>
+        <v>198.63502693555213</v>
       </c>
       <c r="P4" s="12">
         <f t="shared" si="2"/>
-        <v>314.60572313906039</v>
+        <v>345.97245227034989</v>
       </c>
       <c r="Q4" s="12">
         <f t="shared" si="2"/>
-        <v>144.73878741279162</v>
+        <v>193.40520366489352</v>
       </c>
       <c r="R4" s="12">
         <f t="shared" si="2"/>
-        <v>129.61014336153644</v>
+        <v>175.05470821547141</v>
       </c>
       <c r="S4" s="12">
         <f t="shared" si="2"/>
-        <v>108.84140820767014</v>
+        <v>144.42304235010388</v>
       </c>
       <c r="T4" s="13">
         <f>[1]Model!$AW$6</f>
-        <v>64034.32</v>
+        <v>73266.949999999983</v>
       </c>
       <c r="U4" s="26">
         <f>G4/T4</f>
-        <v>15.272244633815118</v>
+        <v>19.224506766011149</v>
       </c>
       <c r="V4" s="14">
         <f>[1]Model!$AP$36</f>
@@ -2503,7 +2510,7 @@
       </c>
       <c r="AA4" s="14">
         <f>[1]Model!$BJ$37</f>
-        <v>-0.69705744731799135</v>
+        <v>-0.79546859376188694</v>
       </c>
       <c r="AB4" s="14" t="str">
         <f>[1]Model!$BJ$38</f>
@@ -2514,11 +2521,11 @@
       </c>
       <c r="AE4" s="16">
         <f>[1]Main!$E$3</f>
-        <v>45862</v>
+        <v>45956</v>
       </c>
       <c r="AF4" s="16">
         <f>[1]Main!$G$3</f>
-        <v>45945</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="5" spans="2:32" x14ac:dyDescent="0.3">
@@ -2760,7 +2767,7 @@
       </c>
     </row>
     <row r="7" spans="2:32" x14ac:dyDescent="0.3">
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="33" t="s">
         <v>23</v>
       </c>
       <c r="C7" s="15" t="s">
@@ -2768,11 +2775,11 @@
       </c>
       <c r="D7" s="10">
         <f>[4]Main!$D$3</f>
-        <v>52.41</v>
+        <v>69.5</v>
       </c>
       <c r="E7" s="11">
         <f>[4]Main!$D$5</f>
-        <v>49899.561000000002</v>
+        <v>64836.549999999996</v>
       </c>
       <c r="F7" s="11">
         <f>[4]Main!$D$8</f>
@@ -2780,7 +2787,7 @@
       </c>
       <c r="G7" s="11">
         <f>[4]Main!$D$9</f>
-        <v>155088.56099999999</v>
+        <v>170025.55</v>
       </c>
       <c r="H7" s="11">
         <f>[4]Model!AO$16</f>
@@ -2808,27 +2815,27 @@
       </c>
       <c r="N7" s="12">
         <f t="shared" si="9"/>
-        <v>15.312851599526065</v>
+        <v>16.787672788309635</v>
       </c>
       <c r="O7" s="12">
         <f t="shared" si="9"/>
-        <v>25.809379430853717</v>
+        <v>28.295148943251785</v>
       </c>
       <c r="P7" s="12">
         <f t="shared" si="9"/>
-        <v>15.10019375785672</v>
+        <v>16.554533308140993</v>
       </c>
       <c r="Q7" s="12">
         <f t="shared" si="9"/>
-        <v>14.688265411537513</v>
+        <v>16.102931054616221</v>
       </c>
       <c r="R7" s="12">
         <f t="shared" si="9"/>
-        <v>14.322481218162107</v>
+        <v>15.701917219302088</v>
       </c>
       <c r="S7" s="12">
         <f t="shared" si="9"/>
-        <v>13.992354912472912</v>
+        <v>15.339995577032976</v>
       </c>
       <c r="T7" s="28">
         <f>[4]Model!$AO$3</f>
@@ -2836,7 +2843,7 @@
       </c>
       <c r="U7" s="31">
         <f t="shared" si="10"/>
-        <v>0.90250672710978685</v>
+        <v>0.98942953410691215</v>
       </c>
       <c r="V7" s="14">
         <f>[4]Model!AN$23</f>
@@ -2860,7 +2867,7 @@
       </c>
       <c r="AA7" s="14">
         <f>[4]Model!$BD$31</f>
-        <v>-0.1271295548656699</v>
+        <v>-0.32822070233413636</v>
       </c>
       <c r="AB7" s="14" t="str">
         <f>[4]Model!$BD$32</f>
@@ -2871,11 +2878,11 @@
       </c>
       <c r="AE7" s="16">
         <f>[4]Main!$E$3</f>
-        <v>45863</v>
+        <v>45957</v>
       </c>
       <c r="AF7" s="16">
         <f>[4]Main!$G$3</f>
-        <v>45951</v>
+        <v>46049</v>
       </c>
     </row>
     <row r="8" spans="2:32" x14ac:dyDescent="0.3">
@@ -2887,11 +2894,11 @@
       </c>
       <c r="D8" s="10">
         <f>[5]Main!$D$3</f>
-        <v>10.67</v>
+        <v>13.76</v>
       </c>
       <c r="E8" s="11">
         <f>[5]Main!$D$5</f>
-        <v>42466.6</v>
+        <v>54709.760000000002</v>
       </c>
       <c r="F8" s="11">
         <f>[5]Main!$D$8</f>
@@ -2899,7 +2906,7 @@
       </c>
       <c r="G8" s="11">
         <f>E8-F8</f>
-        <v>155819.6</v>
+        <v>168062.76</v>
       </c>
       <c r="H8" s="11">
         <f>[5]Model!AO$13</f>
@@ -2911,43 +2918,43 @@
       </c>
       <c r="J8" s="11">
         <f>[5]Model!AQ$13</f>
-        <v>1239.4415999999778</v>
+        <v>3627.3646399999848</v>
       </c>
       <c r="K8" s="11">
         <f>[5]Model!AR$13</f>
-        <v>4261.1494255000007</v>
+        <v>4391.6180773600036</v>
       </c>
       <c r="L8" s="11">
         <f>[5]Model!AS$13</f>
-        <v>6642.8283350600059</v>
+        <v>7062.2854109840036</v>
       </c>
       <c r="M8" s="11">
         <f>[5]Model!AT$13</f>
-        <v>7185.6523113568019</v>
+        <v>7624.8583346045261</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" si="9"/>
-        <v>35.845318610536005</v>
+        <v>38.661780538302281</v>
       </c>
       <c r="O8" s="12">
         <f t="shared" si="9"/>
-        <v>26.504439530532405</v>
+        <v>28.586963769348529</v>
       </c>
       <c r="P8" s="12">
         <f t="shared" si="9"/>
-        <v>125.71758120753958</v>
+        <v>46.331917708719992</v>
       </c>
       <c r="Q8" s="12">
         <f t="shared" si="9"/>
-        <v>36.567504314100937</v>
+        <v>38.268983559023418</v>
       </c>
       <c r="R8" s="12">
         <f t="shared" si="9"/>
-        <v>23.456815702673499</v>
+        <v>23.79722005267746</v>
       </c>
       <c r="S8" s="12">
         <f t="shared" si="9"/>
-        <v>21.684823207174908</v>
+        <v>22.041427214098768</v>
       </c>
       <c r="T8" s="28">
         <f>[5]Model!$AO$3</f>
@@ -2955,7 +2962,7 @@
       </c>
       <c r="U8" s="31">
         <f t="shared" si="10"/>
-        <v>0.88437888427899269</v>
+        <v>0.95386688309845569</v>
       </c>
       <c r="V8" s="14">
         <f>[5]Model!$AN$21</f>
@@ -2979,7 +2986,7 @@
       </c>
       <c r="AA8" s="14">
         <f>[5]Model!$BD$26</f>
-        <v>-0.61304644993749069</v>
+        <v>-0.51829813263956948</v>
       </c>
       <c r="AB8" s="14" t="str">
         <f>[5]Model!$BD$27</f>
@@ -2990,11 +2997,11 @@
       </c>
       <c r="AE8" s="16">
         <f>[5]Main!$E$3</f>
-        <v>45869</v>
+        <v>45957</v>
       </c>
       <c r="AF8" s="16">
         <f>[5]Main!$G$3</f>
-        <v>45952</v>
+        <v>46063</v>
       </c>
     </row>
     <row r="9" spans="2:32" x14ac:dyDescent="0.3">
@@ -3363,11 +3370,11 @@
       </c>
       <c r="D12" s="24">
         <f>[9]Main!$D$3</f>
-        <v>41.45</v>
+        <v>48.41</v>
       </c>
       <c r="E12" s="11">
         <f>[9]Main!$D$5</f>
-        <v>37760.950000000004</v>
+        <v>44101.509999999995</v>
       </c>
       <c r="F12" s="11">
         <f>[9]Main!$D$8</f>
@@ -3375,7 +3382,7 @@
       </c>
       <c r="G12" s="11">
         <f>[9]Main!$D$9</f>
-        <v>40288.950000000004</v>
+        <v>46629.509999999995</v>
       </c>
       <c r="H12" s="11">
         <f>[9]Model!V$49</f>
@@ -3387,43 +3394,43 @@
       </c>
       <c r="J12" s="11">
         <f>[9]Model!X$49</f>
-        <v>2058.3172399999958</v>
+        <v>187.69510000000761</v>
       </c>
       <c r="K12" s="11">
         <f>[9]Model!Y$49</f>
-        <v>3097.2513473999998</v>
+        <v>3128.7290790000015</v>
       </c>
       <c r="L12" s="11">
         <f>[9]Model!Z$49</f>
-        <v>3707.8589376360001</v>
+        <v>3741.0556692600021</v>
       </c>
       <c r="M12" s="11">
         <f>[9]Model!AA$49</f>
-        <v>4061.902063665601</v>
+        <v>4096.4204070720016</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" ref="N12" si="18">$G12/H12</f>
-        <v>7.8139934057408853</v>
+        <v>9.0437373933281595</v>
       </c>
       <c r="O12" s="12">
         <f t="shared" ref="O12" si="19">$G12/I12</f>
-        <v>11.213178402449207</v>
+        <v>12.977876426384634</v>
       </c>
       <c r="P12" s="12">
         <f t="shared" ref="P12" si="20">$G12/J12</f>
-        <v>19.573731987009005</v>
+        <v>248.43221799609103</v>
       </c>
       <c r="Q12" s="12">
         <f t="shared" ref="Q12" si="21">$G12/K12</f>
-        <v>13.007969157498543</v>
+        <v>14.903658585518574</v>
       </c>
       <c r="R12" s="12">
         <f t="shared" ref="R12" si="22">$G12/L12</f>
-        <v>10.865825986812437</v>
+        <v>12.464265202774575</v>
       </c>
       <c r="S12" s="12">
         <f t="shared" ref="S12" si="23">$G12/M12</f>
-        <v>9.9187398830689339</v>
+        <v>11.382989382510514</v>
       </c>
       <c r="T12" s="30">
         <f>[9]Model!$V$30</f>
@@ -3431,7 +3438,7 @@
       </c>
       <c r="U12" s="31">
         <f t="shared" ref="U12:U13" si="24">G12/T12</f>
-        <v>0.99405255366395273</v>
+        <v>1.1504937083641746</v>
       </c>
       <c r="V12" s="14">
         <f>[9]Model!$W$53</f>
@@ -3439,15 +3446,15 @@
       </c>
       <c r="W12" s="14">
         <f>[9]Model!$X$53</f>
-        <v>-6.0456303170920433E-2</v>
+        <v>-5.8914003442856022E-2</v>
       </c>
       <c r="X12" s="14">
         <f>[9]Model!$X$54</f>
-        <v>0.21190611563067488</v>
+        <v>0.12996900975702236</v>
       </c>
       <c r="Y12" s="14">
         <f>[9]Model!$X$57</f>
-        <v>7.9327525715133795E-2</v>
+        <v>4.5595422245376356E-3</v>
       </c>
       <c r="Z12" s="14">
         <f>[9]Model!$AK$56</f>
@@ -3455,22 +3462,22 @@
       </c>
       <c r="AA12" s="14">
         <f>[9]Model!$AK$62</f>
-        <v>0.32757142189307098</v>
+        <v>0.10692975287950546</v>
       </c>
       <c r="AB12" s="14" t="str">
         <f>[9]Model!$AK$63</f>
-        <v>Undervalued</v>
+        <v>Fairly valued</v>
       </c>
       <c r="AC12" s="15">
         <v>1931</v>
       </c>
       <c r="AE12" s="16">
         <f>[9]Main!$E$3</f>
-        <v>45923</v>
+        <v>45957</v>
       </c>
       <c r="AF12" s="16">
         <f>[9]Main!$G$3</f>
-        <v>45954</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="13" spans="2:32" x14ac:dyDescent="0.3">
@@ -3649,11 +3656,11 @@
       </c>
       <c r="D15" s="10">
         <f>[12]Main!$D$3</f>
-        <v>13.57</v>
+        <v>12.68</v>
       </c>
       <c r="E15" s="11">
         <f>[12]Main!$D$5</f>
-        <v>16465.838000000003</v>
+        <v>15385.912</v>
       </c>
       <c r="F15" s="11">
         <f>[12]Main!$D$8</f>
@@ -3661,7 +3668,7 @@
       </c>
       <c r="G15" s="11">
         <f>[12]Main!$D$9</f>
-        <v>13206.838000000003</v>
+        <v>12126.912</v>
       </c>
       <c r="H15" s="11">
         <f>[12]Model!X$21</f>
@@ -3693,7 +3700,7 @@
       </c>
       <c r="U15" s="26">
         <f t="shared" ref="U15:U17" si="26">G15/T15</f>
-        <v>2.3655450474655209</v>
+        <v>2.1721139172487911</v>
       </c>
       <c r="V15" s="14">
         <f>[12]Model!$W$27</f>
@@ -3717,7 +3724,7 @@
       </c>
       <c r="AA15" s="14">
         <f>[12]Model!$AN$82</f>
-        <v>-0.77098230893300101</v>
+        <v>-0.75490772336126366</v>
       </c>
       <c r="AB15" s="14" t="str">
         <f>[12]Model!$AN$38</f>
@@ -3728,7 +3735,7 @@
       </c>
       <c r="AE15" s="16">
         <f>[12]Main!$E$3</f>
-        <v>45899</v>
+        <v>45965</v>
       </c>
       <c r="AF15" s="16">
         <f>[12]Main!$G$3</f>

--- a/Financial Analysis/Models (Automotive).xlsx
+++ b/Financial Analysis/Models (Automotive).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76BED8FC-37D0-49A7-90F7-D63A0AB7A062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759C6A1E-EF91-4C04-8845-FD558E693857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{44A3A52B-B984-4465-AC96-672BE039DB0B}"/>
   </bookViews>
@@ -789,35 +789,35 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>12.68</v>
+            <v>16.350000000000001</v>
           </cell>
           <cell r="E3">
-            <v>45965</v>
+            <v>46002</v>
           </cell>
           <cell r="G3">
-            <v>45966</v>
+            <v>46072</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>15385.912</v>
+            <v>20043.465000000004</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>3259</v>
+            <v>2650</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>12126.912</v>
+            <v>17393.465000000004</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="5">
           <cell r="Z5">
-            <v>5583</v>
+            <v>6308</v>
           </cell>
         </row>
         <row r="21">
@@ -828,16 +828,16 @@
             <v>-4747</v>
           </cell>
           <cell r="Z21">
-            <v>-2883.1596</v>
+            <v>-3460.9900000000007</v>
           </cell>
           <cell r="AA21">
-            <v>-2176.9613879999993</v>
+            <v>-2583.3818999999999</v>
           </cell>
           <cell r="AB21">
-            <v>-1518.9675790080003</v>
+            <v>-1632.3447448000006</v>
           </cell>
           <cell r="AC21">
-            <v>-1276.1137779020798</v>
+            <v>-1191.1187131920003</v>
           </cell>
         </row>
         <row r="27">
@@ -850,7 +850,7 @@
         </row>
         <row r="30">
           <cell r="Z30">
-            <v>0.10388679921189324</v>
+            <v>6.9537095751426664E-2</v>
           </cell>
         </row>
         <row r="31">
@@ -860,17 +860,17 @@
         </row>
         <row r="33">
           <cell r="Z33">
-            <v>-0.53904703564391909</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="AN38" t="str">
-            <v>Heavily overvalued</v>
+            <v>-0.53574508560558032</v>
           </cell>
         </row>
         <row r="82">
           <cell r="AN82">
-            <v>-0.75490772336126366</v>
+            <v>-0.368176647699755</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="AN83" t="str">
+            <v>Overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -893,35 +893,35 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>1.98</v>
+            <v>12.84</v>
           </cell>
           <cell r="E3">
-            <v>45889</v>
+            <v>46002</v>
           </cell>
           <cell r="G3">
-            <v>45972</v>
+            <v>46084</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>6083.55</v>
+            <v>4162.7280000000001</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>1563.6</v>
+            <v>952.79999999999973</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>4519.9500000000007</v>
+            <v>3209.9280000000003</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="6">
           <cell r="AD6">
-            <v>1191.3249999999998</v>
+            <v>1217.925</v>
           </cell>
         </row>
         <row r="17">
@@ -932,16 +932,16 @@
             <v>-2714.0000000000005</v>
           </cell>
           <cell r="AD17">
-            <v>-1573.4800000000002</v>
+            <v>-2107.2950000000001</v>
           </cell>
           <cell r="AE17">
-            <v>-1338.9207800000001</v>
+            <v>-1922.5482500000001</v>
           </cell>
           <cell r="AF17">
-            <v>-909.73493530000019</v>
+            <v>-1480.4593450000002</v>
           </cell>
           <cell r="AG17">
-            <v>-460.13275752800018</v>
+            <v>-983.38917470000047</v>
           </cell>
         </row>
         <row r="26">
@@ -964,12 +964,12 @@
         </row>
         <row r="31">
           <cell r="AD31">
-            <v>-2.3225232409292178</v>
+            <v>-2.4322474700823125</v>
           </cell>
         </row>
         <row r="34">
           <cell r="AQ34">
-            <v>-0.1348443553182711</v>
+            <v>-0.74545542983531754</v>
           </cell>
         </row>
         <row r="35">
@@ -1095,50 +1095,50 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>193.01</v>
+            <v>199.06</v>
           </cell>
           <cell r="E3">
-            <v>45904</v>
+            <v>45995</v>
           </cell>
           <cell r="G3">
-            <v>45959</v>
+            <v>46064</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>251548.00289999999</v>
+            <v>259434.89799999999</v>
           </cell>
         </row>
         <row r="10">
           <cell r="D10">
-            <v>-165794.88908367607</v>
+            <v>-155149.08574013051</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="3">
           <cell r="AO3">
-            <v>336849.65383318724</v>
+            <v>322789.76649221423</v>
           </cell>
         </row>
         <row r="17">
           <cell r="AL17">
-            <v>16541.824556671836</v>
+            <v>15851.379466304839</v>
           </cell>
           <cell r="AM17">
-            <v>33341.865012473871</v>
+            <v>31950.197066614975</v>
           </cell>
           <cell r="AN17">
-            <v>32129.215831703863</v>
+            <v>30788.163080700393</v>
           </cell>
           <cell r="AO17">
-            <v>31093.189943334906</v>
+            <v>25018.091700768884</v>
           </cell>
           <cell r="AP17">
-            <v>31960.129021656801</v>
+            <v>25753.299530106349</v>
           </cell>
           <cell r="AQ17">
-            <v>32363.77480878443</v>
+            <v>28552.150388269696</v>
           </cell>
         </row>
         <row r="21">
@@ -1151,12 +1151,12 @@
         </row>
         <row r="22">
           <cell r="AO22">
-            <v>0.19</v>
+            <v>0.17</v>
           </cell>
         </row>
         <row r="23">
           <cell r="AO23">
-            <v>9.2356294694349347E-2</v>
+            <v>7.2356294694349357E-2</v>
           </cell>
         </row>
         <row r="24">
@@ -1166,7 +1166,7 @@
         </row>
         <row r="30">
           <cell r="BA30">
-            <v>0.7738605857035239</v>
+            <v>0.62176242653210889</v>
           </cell>
         </row>
         <row r="31">
@@ -2362,15 +2362,15 @@
       </c>
       <c r="Q3" s="6">
         <f t="shared" si="0"/>
-        <v>15.985060049740932</v>
+        <v>16.47609346578195</v>
       </c>
       <c r="R3" s="6">
         <f t="shared" si="0"/>
-        <v>16.47293837543743</v>
+        <v>16.605061334187834</v>
       </c>
       <c r="S3" s="6">
         <f t="shared" si="0"/>
-        <v>13.705835387570835</v>
+        <v>14.247457217388808</v>
       </c>
       <c r="T3" s="4"/>
       <c r="U3" s="27">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="X3" s="7">
         <f t="shared" si="1"/>
-        <v>0.17560646577683295</v>
+        <v>0.17144349332239486</v>
       </c>
       <c r="Y3" s="7">
         <f t="shared" si="1"/>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="AA3" s="7">
         <f t="shared" si="1"/>
-        <v>-0.24824550873827725</v>
+        <v>-0.30225003994070132</v>
       </c>
       <c r="AB3" s="8" t="str">
         <f>INDEX(AB4:AB17,MODE(MATCH(AB4:AB17,AB4:AB17,0)))</f>
@@ -2537,75 +2537,75 @@
       </c>
       <c r="D5" s="10">
         <f>[2]Main!$D$3</f>
-        <v>193.01</v>
+        <v>199.06</v>
       </c>
       <c r="E5" s="11">
         <f>[2]Main!$D$5</f>
-        <v>251548.00289999999</v>
+        <v>259434.89799999999</v>
       </c>
       <c r="F5" s="11">
         <f>[2]Main!$D$10</f>
-        <v>-165794.88908367607</v>
+        <v>-155149.08574013051</v>
       </c>
       <c r="G5" s="11">
         <f>E5-F5</f>
-        <v>417342.89198367606</v>
+        <v>414583.9837401305</v>
       </c>
       <c r="H5" s="11">
         <f>[2]Model!AL$17</f>
-        <v>16541.824556671836</v>
+        <v>15851.379466304839</v>
       </c>
       <c r="I5" s="11">
         <f>[2]Model!AM$17</f>
-        <v>33341.865012473871</v>
+        <v>31950.197066614975</v>
       </c>
       <c r="J5" s="11">
         <f>[2]Model!AN$17</f>
-        <v>32129.215831703863</v>
+        <v>30788.163080700393</v>
       </c>
       <c r="K5" s="11">
         <f>[2]Model!AO$17</f>
-        <v>31093.189943334906</v>
+        <v>25018.091700768884</v>
       </c>
       <c r="L5" s="11">
         <f>[2]Model!AP$17</f>
-        <v>31960.129021656801</v>
+        <v>25753.299530106349</v>
       </c>
       <c r="M5" s="11">
         <f>[2]Model!AQ$17</f>
-        <v>32363.77480878443</v>
+        <v>28552.150388269696</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" ref="N5" si="3">$G5/H5</f>
-        <v>25.229556180690395</v>
+        <v>26.154441928628902</v>
       </c>
       <c r="O5" s="12">
         <f t="shared" ref="O5" si="4">$G5/I5</f>
-        <v>12.517083007430436</v>
+        <v>12.975944494981933</v>
       </c>
       <c r="P5" s="12">
         <f t="shared" ref="P5" si="5">$G5/J5</f>
-        <v>12.989513786136614</v>
+        <v>13.465694028365501</v>
       </c>
       <c r="Q5" s="12">
         <f t="shared" ref="Q5" si="6">$G5/K5</f>
-        <v>13.422324719472442</v>
+        <v>16.571367180950457</v>
       </c>
       <c r="R5" s="12">
         <f t="shared" ref="R5" si="7">$G5/L5</f>
-        <v>13.058235519039252</v>
+        <v>16.098286095553306</v>
       </c>
       <c r="S5" s="12">
         <f t="shared" ref="S5" si="8">$G5/M5</f>
-        <v>12.895371273884825</v>
+        <v>14.520236763338753</v>
       </c>
       <c r="T5" s="13">
         <f>[2]Model!$AO$3</f>
-        <v>336849.65383318724</v>
+        <v>322789.76649221423</v>
       </c>
       <c r="U5" s="26">
         <f>G5/T5</f>
-        <v>1.2389589457329537</v>
+        <v>1.2843777181831146</v>
       </c>
       <c r="V5" s="14">
         <f>[2]Model!AN$21</f>
@@ -2617,11 +2617,11 @@
       </c>
       <c r="X5" s="14">
         <f>[2]Model!$AO$22</f>
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="Y5" s="14">
         <f>[2]Model!$AO$23</f>
-        <v>9.2356294694349347E-2</v>
+        <v>7.2356294694349357E-2</v>
       </c>
       <c r="Z5" s="14">
         <f>[2]Model!$BA$24</f>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="AA5" s="14">
         <f>[2]Model!$BA$30</f>
-        <v>0.7738605857035239</v>
+        <v>0.62176242653210889</v>
       </c>
       <c r="AB5" s="14" t="str">
         <f>[2]Model!$BA$31</f>
@@ -2640,11 +2640,11 @@
       </c>
       <c r="AE5" s="16">
         <f>[2]Main!$E$3</f>
-        <v>45904</v>
+        <v>45995</v>
       </c>
       <c r="AF5" s="16">
         <f>[2]Main!$G$3</f>
-        <v>45959</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="6" spans="2:32" x14ac:dyDescent="0.3">
@@ -3656,19 +3656,19 @@
       </c>
       <c r="D15" s="10">
         <f>[12]Main!$D$3</f>
-        <v>12.68</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="E15" s="11">
         <f>[12]Main!$D$5</f>
-        <v>15385.912</v>
+        <v>20043.465000000004</v>
       </c>
       <c r="F15" s="11">
         <f>[12]Main!$D$8</f>
-        <v>3259</v>
+        <v>2650</v>
       </c>
       <c r="G15" s="11">
         <f>[12]Main!$D$9</f>
-        <v>12126.912</v>
+        <v>17393.465000000004</v>
       </c>
       <c r="H15" s="11">
         <f>[12]Model!X$21</f>
@@ -3680,27 +3680,27 @@
       </c>
       <c r="J15" s="11">
         <f>[12]Model!Z$21</f>
-        <v>-2883.1596</v>
+        <v>-3460.9900000000007</v>
       </c>
       <c r="K15" s="11">
         <f>[12]Model!AA$21</f>
-        <v>-2176.9613879999993</v>
+        <v>-2583.3818999999999</v>
       </c>
       <c r="L15" s="11">
         <f>[12]Model!AB$21</f>
-        <v>-1518.9675790080003</v>
+        <v>-1632.3447448000006</v>
       </c>
       <c r="M15" s="11">
         <f>[12]Model!AC$21</f>
-        <v>-1276.1137779020798</v>
+        <v>-1191.1187131920003</v>
       </c>
       <c r="T15" s="13">
         <f>[12]Model!$Z$5</f>
-        <v>5583</v>
+        <v>6308</v>
       </c>
       <c r="U15" s="26">
         <f t="shared" ref="U15:U17" si="26">G15/T15</f>
-        <v>2.1721139172487911</v>
+        <v>2.7573660431198483</v>
       </c>
       <c r="V15" s="14">
         <f>[12]Model!$W$27</f>
@@ -3712,11 +3712,11 @@
       </c>
       <c r="X15" s="14">
         <f>[12]Model!$Z$30</f>
-        <v>0.10388679921189324</v>
+        <v>6.9537095751426664E-2</v>
       </c>
       <c r="Y15" s="14">
         <f>[12]Model!$Z$33</f>
-        <v>-0.53904703564391909</v>
+        <v>-0.53574508560558032</v>
       </c>
       <c r="Z15" s="14">
         <f>[12]Model!$AN$31</f>
@@ -3724,22 +3724,22 @@
       </c>
       <c r="AA15" s="14">
         <f>[12]Model!$AN$82</f>
-        <v>-0.75490772336126366</v>
+        <v>-0.368176647699755</v>
       </c>
       <c r="AB15" s="14" t="str">
-        <f>[12]Model!$AN$38</f>
-        <v>Heavily overvalued</v>
+        <f>[12]Model!$AN$83</f>
+        <v>Overvalued</v>
       </c>
       <c r="AC15" s="15">
         <v>2009</v>
       </c>
       <c r="AE15" s="16">
         <f>[12]Main!$E$3</f>
-        <v>45965</v>
+        <v>46002</v>
       </c>
       <c r="AF15" s="16">
         <f>[12]Main!$G$3</f>
-        <v>45966</v>
+        <v>46072</v>
       </c>
     </row>
     <row r="16" spans="2:32" x14ac:dyDescent="0.3">
@@ -3751,19 +3751,19 @@
       </c>
       <c r="D16" s="10">
         <f>[13]Main!$D$3</f>
-        <v>1.98</v>
+        <v>12.84</v>
       </c>
       <c r="E16" s="11">
         <f>[13]Main!$D$5</f>
-        <v>6083.55</v>
+        <v>4162.7280000000001</v>
       </c>
       <c r="F16" s="11">
         <f>[13]Main!$D$8</f>
-        <v>1563.6</v>
+        <v>952.79999999999973</v>
       </c>
       <c r="G16" s="11">
         <f>[13]Main!$D$9</f>
-        <v>4519.9500000000007</v>
+        <v>3209.9280000000003</v>
       </c>
       <c r="H16" s="11">
         <f>[13]Model!AB$17</f>
@@ -3775,27 +3775,27 @@
       </c>
       <c r="J16" s="11">
         <f>[13]Model!AD$17</f>
-        <v>-1573.4800000000002</v>
+        <v>-2107.2950000000001</v>
       </c>
       <c r="K16" s="11">
         <f>[13]Model!AE$17</f>
-        <v>-1338.9207800000001</v>
+        <v>-1922.5482500000001</v>
       </c>
       <c r="L16" s="11">
         <f>[13]Model!AF$17</f>
-        <v>-909.73493530000019</v>
+        <v>-1480.4593450000002</v>
       </c>
       <c r="M16" s="11">
         <f>[13]Model!AG$17</f>
-        <v>-460.13275752800018</v>
+        <v>-983.38917470000047</v>
       </c>
       <c r="T16" s="13">
         <f>[13]Model!$AD$6</f>
-        <v>1191.3249999999998</v>
+        <v>1217.925</v>
       </c>
       <c r="U16" s="26">
         <f t="shared" si="26"/>
-        <v>3.7940528403248495</v>
+        <v>2.6355711558593513</v>
       </c>
       <c r="V16" s="14">
         <f>[13]Model!$AA$26</f>
@@ -3811,7 +3811,7 @@
       </c>
       <c r="Y16" s="14">
         <f>[13]Model!$AD$31</f>
-        <v>-2.3225232409292178</v>
+        <v>-2.4322474700823125</v>
       </c>
       <c r="Z16" s="14">
         <f>[13]Model!$AQ$28</f>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="AA16" s="14">
         <f>[13]Model!$AQ$34</f>
-        <v>-0.1348443553182711</v>
+        <v>-0.74545542983531754</v>
       </c>
       <c r="AB16" s="14" t="str">
         <f>[13]Model!$AQ$35</f>
@@ -3830,11 +3830,11 @@
       </c>
       <c r="AE16" s="16">
         <f>[13]Main!$E$3</f>
-        <v>45889</v>
+        <v>46002</v>
       </c>
       <c r="AF16" s="16">
         <f>[13]Main!$G$3</f>
-        <v>45972</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="17" spans="2:32" x14ac:dyDescent="0.3">

--- a/Financial Analysis/Models (Automotive).xlsx
+++ b/Financial Analysis/Models (Automotive).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759C6A1E-EF91-4C04-8845-FD558E693857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD816FB-EF5D-4128-8076-1962747AF527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{44A3A52B-B984-4465-AC96-672BE039DB0B}"/>
   </bookViews>
@@ -528,83 +528,70 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>433.72</v>
+            <v>426.3</v>
           </cell>
           <cell r="E3">
-            <v>45956</v>
+            <v>46052</v>
           </cell>
           <cell r="G3">
-            <v>46050</v>
+            <v>46140</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>1442465.9760000003</v>
+            <v>1417788.54</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>33945</v>
+            <v>35683</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="6">
-          <cell r="AW6">
-            <v>73266.949999999983</v>
+          <cell r="BB6">
+            <v>46285</v>
           </cell>
         </row>
         <row r="27">
-          <cell r="AU27">
+          <cell r="AZ27">
+            <v>-862</v>
+          </cell>
+          <cell r="BA27">
+            <v>719</v>
+          </cell>
+          <cell r="BB27">
+            <v>5519</v>
+          </cell>
+          <cell r="BC27">
+            <v>12556</v>
+          </cell>
+          <cell r="BD27">
             <v>14997</v>
           </cell>
-          <cell r="AV27">
+          <cell r="BE27">
             <v>7091</v>
           </cell>
-          <cell r="AW27">
-            <v>4071.1940119999881</v>
-          </cell>
-          <cell r="AX27">
-            <v>7282.7460136000045</v>
-          </cell>
-          <cell r="AY27">
-            <v>8046.1759089979996</v>
-          </cell>
-          <cell r="AZ27">
-            <v>9752.7441125739933</v>
-          </cell>
         </row>
         <row r="31">
-          <cell r="BJ31">
-            <v>0.05</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="AP36">
-            <v>0.82516435758086049</v>
-          </cell>
-          <cell r="AQ36">
-            <v>0.14528823258046342</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="BJ37">
-            <v>-0.79546859376188694</v>
+          <cell r="BO31">
+            <v>3.0000000000000027E-2</v>
           </cell>
         </row>
         <row r="38">
-          <cell r="BJ38" t="str">
-            <v>Heavily overvalued</v>
+          <cell r="BO38">
+            <v>0.19999999999999996</v>
           </cell>
         </row>
         <row r="42">
-          <cell r="AU42">
-            <v>0.18248891736331416</v>
+          <cell r="AZ42">
+            <v>0.1655545609895028</v>
           </cell>
         </row>
         <row r="45">
-          <cell r="AU45">
-            <v>9.1874799789197395E-2</v>
+          <cell r="AZ45">
+            <v>-2.8073887216209618E-3</v>
           </cell>
         </row>
       </sheetData>
@@ -789,88 +776,88 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="D3">
-            <v>16.350000000000001</v>
+            <v>15.22</v>
           </cell>
           <cell r="E3">
-            <v>46002</v>
+            <v>46076</v>
           </cell>
           <cell r="G3">
-            <v>46072</v>
+            <v>46154</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>20043.465000000004</v>
+            <v>18888.02</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>2650</v>
+            <v>3259</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>17393.465000000004</v>
+            <v>15629.02</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
-        <row r="5">
-          <cell r="Z5">
-            <v>6308</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="X21">
+        <row r="8">
+          <cell r="AD8">
+            <v>5387</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="AB24">
             <v>-5432</v>
           </cell>
-          <cell r="Y21">
+          <cell r="AC24">
             <v>-4747</v>
           </cell>
-          <cell r="Z21">
-            <v>-3460.9900000000007</v>
-          </cell>
-          <cell r="AA21">
-            <v>-2583.3818999999999</v>
-          </cell>
-          <cell r="AB21">
-            <v>-1632.3447448000006</v>
-          </cell>
-          <cell r="AC21">
-            <v>-1191.1187131920003</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="W27">
+          <cell r="AD24">
+            <v>-3648</v>
+          </cell>
+          <cell r="AE24">
+            <v>-2627.28</v>
+          </cell>
+          <cell r="AF24">
+            <v>-1731.889999999999</v>
+          </cell>
+          <cell r="AG24">
+            <v>-1353.9353432000007</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="AA30">
             <v>29.145454545454545</v>
           </cell>
-          <cell r="X27">
+          <cell r="AB30">
             <v>1.6743063932448732</v>
           </cell>
         </row>
-        <row r="30">
-          <cell r="Z30">
-            <v>6.9537095751426664E-2</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="AN31">
+        <row r="33">
+          <cell r="AD33">
+            <v>2.6731019120103953E-2</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="AR34">
             <v>0.09</v>
           </cell>
         </row>
-        <row r="33">
-          <cell r="Z33">
-            <v>-0.53574508560558032</v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="AN82">
-            <v>-0.368176647699755</v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="AN83" t="str">
-            <v>Overvalued</v>
+        <row r="36">
+          <cell r="AD36">
+            <v>-0.66549099684425472</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="AR86">
+            <v>-0.6528076655759868</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="AR87" t="str">
+            <v>Heavily overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -896,85 +883,85 @@
             <v>12.84</v>
           </cell>
           <cell r="E3">
-            <v>46002</v>
+            <v>46078</v>
           </cell>
           <cell r="G3">
-            <v>46084</v>
+            <v>46153</v>
           </cell>
         </row>
         <row r="5">
           <cell r="D5">
-            <v>4162.7280000000001</v>
+            <v>4173</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>952.79999999999973</v>
+            <v>-577.19999999999982</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>3209.9280000000003</v>
+            <v>4750.2</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="6">
-          <cell r="AD6">
-            <v>1217.925</v>
+          <cell r="AH6">
+            <v>1353.7</v>
           </cell>
         </row>
         <row r="17">
-          <cell r="AB17">
+          <cell r="AF17">
             <v>-2828.3</v>
           </cell>
-          <cell r="AC17">
+          <cell r="AG17">
             <v>-2714.0000000000005</v>
           </cell>
-          <cell r="AD17">
-            <v>-2107.2950000000001</v>
-          </cell>
-          <cell r="AE17">
-            <v>-1922.5482500000001</v>
-          </cell>
-          <cell r="AF17">
-            <v>-1480.4593450000002</v>
-          </cell>
-          <cell r="AG17">
-            <v>-983.38917470000047</v>
+          <cell r="AH17">
+            <v>-2698.1</v>
+          </cell>
+          <cell r="AI17">
+            <v>-2656.8310000000001</v>
+          </cell>
+          <cell r="AJ17">
+            <v>-2272.0624100000005</v>
+          </cell>
+          <cell r="AK17">
+            <v>-1589.9733691000001</v>
           </cell>
         </row>
         <row r="26">
-          <cell r="AA26">
+          <cell r="AE26">
             <v>21.44280442804428</v>
           </cell>
-          <cell r="AB26">
+          <cell r="AF26">
             <v>-2.1210128247287185E-2</v>
           </cell>
         </row>
         <row r="27">
-          <cell r="AD27">
-            <v>-0.6</v>
+          <cell r="AH27">
+            <v>-0.92819679397207633</v>
           </cell>
         </row>
         <row r="28">
-          <cell r="AQ28">
+          <cell r="AU28">
             <v>0.09</v>
           </cell>
         </row>
         <row r="31">
-          <cell r="AD31">
-            <v>-2.4322474700823125</v>
+          <cell r="AH31">
+            <v>-2.5868360788948808</v>
           </cell>
         </row>
         <row r="34">
-          <cell r="AQ34">
-            <v>-0.74545542983531754</v>
+          <cell r="AU34">
+            <v>-0.65161272552498328</v>
           </cell>
         </row>
         <row r="35">
-          <cell r="AQ35" t="str">
-            <v>Slightly overvalued</v>
+          <cell r="AU35" t="str">
+            <v>Heavily overvalued</v>
           </cell>
         </row>
       </sheetData>
@@ -2350,7 +2337,7 @@
       <c r="M3" s="4"/>
       <c r="N3" s="6">
         <f t="shared" ref="N3:U3" si="0">TRIMMEAN(N4:N1048576,80%)</f>
-        <v>15.016831977855155</v>
+        <v>13.72094137593777</v>
       </c>
       <c r="O3" s="6">
         <f t="shared" si="0"/>
@@ -2379,19 +2366,19 @@
       </c>
       <c r="V3" s="7">
         <f t="shared" ref="V3:AA3" si="1">TRIMMEAN(V4:V1048576,80%)</f>
-        <v>0.19267638552711031</v>
+        <v>0.14365826885951449</v>
       </c>
       <c r="W3" s="7">
         <f t="shared" si="1"/>
-        <v>8.0724152757208303E-2</v>
+        <v>6.1928946411040187E-2</v>
       </c>
       <c r="X3" s="7">
         <f t="shared" si="1"/>
-        <v>0.17144349332239486</v>
+        <v>0.1674421953656636</v>
       </c>
       <c r="Y3" s="7">
         <f t="shared" si="1"/>
-        <v>4.4141096704330883E-2</v>
+        <v>2.7624996362057151E-2</v>
       </c>
       <c r="Z3" s="7">
         <f t="shared" si="1"/>
@@ -2399,7 +2386,7 @@
       </c>
       <c r="AA3" s="7">
         <f t="shared" si="1"/>
-        <v>-0.30225003994070132</v>
+        <v>-0.21453441990870947</v>
       </c>
       <c r="AB3" s="8" t="str">
         <f>INDEX(AB4:AB17,MODE(MATCH(AB4:AB17,AB4:AB17,0)))</f>
@@ -2418,114 +2405,114 @@
       </c>
       <c r="D4" s="10">
         <f>[1]Main!$D$3</f>
-        <v>433.72</v>
+        <v>426.3</v>
       </c>
       <c r="E4" s="11">
         <f>[1]Main!$D$5</f>
-        <v>1442465.9760000003</v>
+        <v>1417788.54</v>
       </c>
       <c r="F4" s="11">
         <f>[1]Main!$D$8</f>
-        <v>33945</v>
+        <v>35683</v>
       </c>
       <c r="G4" s="11">
         <f>E4-F4</f>
-        <v>1408520.9760000003</v>
+        <v>1382105.54</v>
       </c>
       <c r="H4" s="11">
-        <f>[1]Model!AU$27</f>
+        <f>[1]Model!AZ$27</f>
+        <v>-862</v>
+      </c>
+      <c r="I4" s="11">
+        <f>[1]Model!BA$27</f>
+        <v>719</v>
+      </c>
+      <c r="J4" s="11">
+        <f>[1]Model!BB$27</f>
+        <v>5519</v>
+      </c>
+      <c r="K4" s="11">
+        <f>[1]Model!BC$27</f>
+        <v>12556</v>
+      </c>
+      <c r="L4" s="11">
+        <f>[1]Model!BD$27</f>
         <v>14997</v>
       </c>
-      <c r="I4" s="11">
-        <f>[1]Model!AV$27</f>
+      <c r="M4" s="11">
+        <f>[1]Model!BE$27</f>
         <v>7091</v>
-      </c>
-      <c r="J4" s="11">
-        <f>[1]Model!AW$27</f>
-        <v>4071.1940119999881</v>
-      </c>
-      <c r="K4" s="11">
-        <f>[1]Model!AX$27</f>
-        <v>7282.7460136000045</v>
-      </c>
-      <c r="L4" s="11">
-        <f>[1]Model!AY$27</f>
-        <v>8046.1759089979996</v>
-      </c>
-      <c r="M4" s="11">
-        <f>[1]Model!AZ$27</f>
-        <v>9752.7441125739933</v>
       </c>
       <c r="N4" s="12">
         <f t="shared" ref="N4:S4" si="2">$G4/H4</f>
-        <v>93.920182436487309</v>
+        <v>-1603.3706960556844</v>
       </c>
       <c r="O4" s="12">
         <f t="shared" si="2"/>
-        <v>198.63502693555213</v>
+        <v>1922.2608344923506</v>
       </c>
       <c r="P4" s="12">
         <f t="shared" si="2"/>
-        <v>345.97245227034989</v>
+        <v>250.42680558072115</v>
       </c>
       <c r="Q4" s="12">
         <f t="shared" si="2"/>
-        <v>193.40520366489352</v>
+        <v>110.07530582988213</v>
       </c>
       <c r="R4" s="12">
         <f t="shared" si="2"/>
-        <v>175.05470821547141</v>
+        <v>92.158801093552043</v>
       </c>
       <c r="S4" s="12">
         <f t="shared" si="2"/>
-        <v>144.42304235010388</v>
+        <v>194.90982089973207</v>
       </c>
       <c r="T4" s="13">
-        <f>[1]Model!$AW$6</f>
-        <v>73266.949999999983</v>
+        <f>[1]Model!$BB$6</f>
+        <v>46285</v>
       </c>
       <c r="U4" s="26">
         <f>G4/T4</f>
-        <v>19.224506766011149</v>
+        <v>29.860765690828561</v>
       </c>
       <c r="V4" s="14">
         <f>[1]Model!$AP$36</f>
-        <v>0.82516435758086049</v>
+        <v>0</v>
       </c>
       <c r="W4" s="14">
         <f>[1]Model!$AQ$36</f>
-        <v>0.14528823258046342</v>
+        <v>0</v>
       </c>
       <c r="X4" s="32">
-        <f>[1]Model!$AU$42</f>
-        <v>0.18248891736331416</v>
+        <f>[1]Model!$AZ$42</f>
+        <v>0.1655545609895028</v>
       </c>
       <c r="Y4" s="32">
-        <f>[1]Model!$AU$45</f>
-        <v>9.1874799789197395E-2</v>
+        <f>[1]Model!$AZ$45</f>
+        <v>-2.8073887216209618E-3</v>
       </c>
       <c r="Z4" s="14">
-        <f>[1]Model!$BJ$31</f>
-        <v>0.05</v>
+        <f>[1]Model!$BO$31</f>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AA4" s="14">
-        <f>[1]Model!$BJ$37</f>
-        <v>-0.79546859376188694</v>
-      </c>
-      <c r="AB4" s="14" t="str">
-        <f>[1]Model!$BJ$38</f>
-        <v>Heavily overvalued</v>
+        <f>[1]Model!$BO$37</f>
+        <v>0</v>
+      </c>
+      <c r="AB4" s="14">
+        <f>[1]Model!$BO$38</f>
+        <v>0.19999999999999996</v>
       </c>
       <c r="AC4" s="15">
         <v>2003</v>
       </c>
       <c r="AE4" s="16">
         <f>[1]Main!$E$3</f>
-        <v>45956</v>
+        <v>46052</v>
       </c>
       <c r="AF4" s="16">
         <f>[1]Main!$G$3</f>
-        <v>46050</v>
+        <v>46140</v>
       </c>
     </row>
     <row r="5" spans="2:32" x14ac:dyDescent="0.3">
@@ -3656,90 +3643,90 @@
       </c>
       <c r="D15" s="10">
         <f>[12]Main!$D$3</f>
-        <v>16.350000000000001</v>
+        <v>15.22</v>
       </c>
       <c r="E15" s="11">
         <f>[12]Main!$D$5</f>
-        <v>20043.465000000004</v>
+        <v>18888.02</v>
       </c>
       <c r="F15" s="11">
         <f>[12]Main!$D$8</f>
-        <v>2650</v>
+        <v>3259</v>
       </c>
       <c r="G15" s="11">
         <f>[12]Main!$D$9</f>
-        <v>17393.465000000004</v>
+        <v>15629.02</v>
       </c>
       <c r="H15" s="11">
-        <f>[12]Model!X$21</f>
+        <f>[12]Model!AB$24</f>
         <v>-5432</v>
       </c>
       <c r="I15" s="11">
-        <f>[12]Model!Y$21</f>
+        <f>[12]Model!AC$24</f>
         <v>-4747</v>
       </c>
       <c r="J15" s="11">
-        <f>[12]Model!Z$21</f>
-        <v>-3460.9900000000007</v>
+        <f>[12]Model!AD$24</f>
+        <v>-3648</v>
       </c>
       <c r="K15" s="11">
-        <f>[12]Model!AA$21</f>
-        <v>-2583.3818999999999</v>
+        <f>[12]Model!AE$24</f>
+        <v>-2627.28</v>
       </c>
       <c r="L15" s="11">
-        <f>[12]Model!AB$21</f>
-        <v>-1632.3447448000006</v>
+        <f>[12]Model!AF$24</f>
+        <v>-1731.889999999999</v>
       </c>
       <c r="M15" s="11">
-        <f>[12]Model!AC$21</f>
-        <v>-1191.1187131920003</v>
+        <f>[12]Model!AG$24</f>
+        <v>-1353.9353432000007</v>
       </c>
       <c r="T15" s="13">
-        <f>[12]Model!$Z$5</f>
-        <v>6308</v>
+        <f>[12]Model!$AD$8</f>
+        <v>5387</v>
       </c>
       <c r="U15" s="26">
         <f t="shared" ref="U15:U17" si="26">G15/T15</f>
-        <v>2.7573660431198483</v>
+        <v>2.9012474475589385</v>
       </c>
       <c r="V15" s="14">
-        <f>[12]Model!$W$27</f>
+        <f>[12]Model!$AA$30</f>
         <v>29.145454545454545</v>
       </c>
       <c r="W15" s="14">
-        <f>[12]Model!$X$27</f>
+        <f>[12]Model!$AB$30</f>
         <v>1.6743063932448732</v>
       </c>
       <c r="X15" s="14">
-        <f>[12]Model!$Z$30</f>
-        <v>6.9537095751426664E-2</v>
+        <f>[12]Model!$AD$33</f>
+        <v>2.6731019120103953E-2</v>
       </c>
       <c r="Y15" s="14">
-        <f>[12]Model!$Z$33</f>
-        <v>-0.53574508560558032</v>
+        <f>[12]Model!$AD$36</f>
+        <v>-0.66549099684425472</v>
       </c>
       <c r="Z15" s="14">
-        <f>[12]Model!$AN$31</f>
+        <f>[12]Model!$AR$34</f>
         <v>0.09</v>
       </c>
       <c r="AA15" s="14">
-        <f>[12]Model!$AN$82</f>
-        <v>-0.368176647699755</v>
+        <f>[12]Model!$AR$86</f>
+        <v>-0.6528076655759868</v>
       </c>
       <c r="AB15" s="14" t="str">
-        <f>[12]Model!$AN$83</f>
-        <v>Overvalued</v>
+        <f>[12]Model!$AR$87</f>
+        <v>Heavily overvalued</v>
       </c>
       <c r="AC15" s="15">
         <v>2009</v>
       </c>
       <c r="AE15" s="16">
         <f>[12]Main!$E$3</f>
-        <v>46002</v>
+        <v>46076</v>
       </c>
       <c r="AF15" s="16">
         <f>[12]Main!$G$3</f>
-        <v>46072</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="16" spans="2:32" x14ac:dyDescent="0.3">
@@ -3755,86 +3742,86 @@
       </c>
       <c r="E16" s="11">
         <f>[13]Main!$D$5</f>
-        <v>4162.7280000000001</v>
+        <v>4173</v>
       </c>
       <c r="F16" s="11">
         <f>[13]Main!$D$8</f>
-        <v>952.79999999999973</v>
+        <v>-577.19999999999982</v>
       </c>
       <c r="G16" s="11">
         <f>[13]Main!$D$9</f>
-        <v>3209.9280000000003</v>
+        <v>4750.2</v>
       </c>
       <c r="H16" s="11">
-        <f>[13]Model!AB$17</f>
+        <f>[13]Model!AF$17</f>
         <v>-2828.3</v>
       </c>
       <c r="I16" s="11">
-        <f>[13]Model!AC$17</f>
+        <f>[13]Model!AG$17</f>
         <v>-2714.0000000000005</v>
       </c>
       <c r="J16" s="11">
-        <f>[13]Model!AD$17</f>
-        <v>-2107.2950000000001</v>
+        <f>[13]Model!AH$17</f>
+        <v>-2698.1</v>
       </c>
       <c r="K16" s="11">
-        <f>[13]Model!AE$17</f>
-        <v>-1922.5482500000001</v>
+        <f>[13]Model!AI$17</f>
+        <v>-2656.8310000000001</v>
       </c>
       <c r="L16" s="11">
-        <f>[13]Model!AF$17</f>
-        <v>-1480.4593450000002</v>
+        <f>[13]Model!AJ$17</f>
+        <v>-2272.0624100000005</v>
       </c>
       <c r="M16" s="11">
-        <f>[13]Model!AG$17</f>
-        <v>-983.38917470000047</v>
+        <f>[13]Model!AK$17</f>
+        <v>-1589.9733691000001</v>
       </c>
       <c r="T16" s="13">
-        <f>[13]Model!$AD$6</f>
-        <v>1217.925</v>
+        <f>[13]Model!$AH$6</f>
+        <v>1353.7</v>
       </c>
       <c r="U16" s="26">
         <f t="shared" si="26"/>
-        <v>2.6355711558593513</v>
+        <v>3.50904927236463</v>
       </c>
       <c r="V16" s="14">
-        <f>[13]Model!$AA$26</f>
+        <f>[13]Model!$AE$26</f>
         <v>21.44280442804428</v>
       </c>
       <c r="W16" s="14">
-        <f>[13]Model!$AB$26</f>
+        <f>[13]Model!$AF$26</f>
         <v>-2.1210128247287185E-2</v>
       </c>
       <c r="X16" s="14">
-        <f>[13]Model!$AD$27</f>
-        <v>-0.6</v>
+        <f>[13]Model!$AH$27</f>
+        <v>-0.92819679397207633</v>
       </c>
       <c r="Y16" s="14">
-        <f>[13]Model!$AD$31</f>
-        <v>-2.4322474700823125</v>
+        <f>[13]Model!$AH$31</f>
+        <v>-2.5868360788948808</v>
       </c>
       <c r="Z16" s="14">
-        <f>[13]Model!$AQ$28</f>
+        <f>[13]Model!$AU$28</f>
         <v>0.09</v>
       </c>
       <c r="AA16" s="14">
-        <f>[13]Model!$AQ$34</f>
-        <v>-0.74545542983531754</v>
+        <f>[13]Model!$AU$34</f>
+        <v>-0.65161272552498328</v>
       </c>
       <c r="AB16" s="14" t="str">
-        <f>[13]Model!$AQ$35</f>
-        <v>Slightly overvalued</v>
+        <f>[13]Model!$AU$35</f>
+        <v>Heavily overvalued</v>
       </c>
       <c r="AC16" s="15">
         <v>2007</v>
       </c>
       <c r="AE16" s="16">
         <f>[13]Main!$E$3</f>
-        <v>46002</v>
+        <v>46078</v>
       </c>
       <c r="AF16" s="16">
         <f>[13]Main!$G$3</f>
-        <v>46084</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="17" spans="2:32" x14ac:dyDescent="0.3">
